--- a/Logic/Milestone_Register_Sep20.xlsx
+++ b/Logic/Milestone_Register_Sep20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EsterMonroyGatell\Documents\GitHub\M-GRAT\Logic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35148C4-7176-4C75-A1B8-5C661DFB497E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59615BF9-78D3-45F1-8C09-ECE6BD4C3F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -369,9 +369,6 @@
     <t>Standardized Asset Registry</t>
   </si>
   <si>
-    <t>A trusted, consistent asset register in Maximo Manage with governance standards, unique asset records, and defined location hierarchy. Single source of truth for all field assets.</t>
-  </si>
-  <si>
     <t>Enables work order linkage, job plan reuse, and downstream analytics. Without a clean asset register, health scoring and inspection scoping cannot be reliably performed.</t>
   </si>
   <si>
@@ -417,9 +414,6 @@
     <t>Equipment Criticality Scored</t>
   </si>
   <si>
-    <t>All maintainable assets classified by criticality tier (Critical / High / Medium / Low) using a repeatable scoring methodology.</t>
-  </si>
-  <si>
     <t>Directs maintenance effort and investment toward highest-impact assets. Ensures critical assets get appropriate scheduling priority. Prerequisite for FMEA prioritization and health scoring.</t>
   </si>
   <si>
@@ -508,9 +502,6 @@
     <t>Asset Hierarchy</t>
   </si>
   <si>
-    <t>Parent-child asset structures and locations defined to show how equipment is organized and related. Enables cost rollups, health/condition rollups, and drill-down maintenance history.</t>
-  </si>
-  <si>
     <t>Enables cost rollups, component-level maintenance history, and failure impact analysis across the asset lifecycle. Unlocks multi-team scheduling and shutdown planning for customers with complex asset networks.</t>
   </si>
   <si>
@@ -547,9 +538,6 @@
     <t>Asset Relationships</t>
   </si>
   <si>
-    <t>Dependencies and relationships between assets and systems modeled in Maximo. Linear asset networks linked to connected systems. Supports system-level maintenance planning and outage/shutdown planning.</t>
-  </si>
-  <si>
     <t>System-level maintenance planning; better outage/shutdown planning; understanding of asset dependencies.</t>
   </si>
   <si>
@@ -581,9 +569,6 @@
   </si>
   <si>
     <t>Job Plans — Basics</t>
-  </si>
-  <si>
-    <t>Job plans exist in Maximo as reusable work templates linked to work orders and PMs. Minimum viable: estimated duration + at least one labor/craft or crew type requirement.</t>
   </si>
   <si>
     <t>Job plans are the reuse mechanism. Without them every work order is created from scratch, increasing planning time and reducing data consistency.</t>
@@ -622,9 +607,6 @@
     <t>Job Plans — Needs</t>
   </si>
   <si>
-    <t>Job plans enriched beyond basic duration + craft to include materials, tools, services, work type classification, and asset/work type specification.</t>
-  </si>
-  <si>
     <t>Better forecast of resources tied to job plans; increased maintenance supervisor and staff productivity.</t>
   </si>
   <si>
@@ -661,9 +643,6 @@
     <t>Job Plans — Asset Relationships</t>
   </si>
   <si>
-    <t>Job plans have native structure — relationships between sub-job plans generating work order hierarchies automatically. Job plans are scoped to specific asset classifications, not generic templates.</t>
-  </si>
-  <si>
     <t>Asset-specific maintenance planning; reusable maintenance strategies scoped to asset class.</t>
   </si>
   <si>
@@ -703,9 +682,6 @@
     <t>Workforce Schedule Optimization</t>
   </si>
   <si>
-    <t>Technician scheduling and dispatch driven by asset condition signals, job urgency, and skill match. Crew assignment accounts for skill, location/proximity, and effective availability.</t>
-  </si>
-  <si>
     <t>Reduces wasted travel time, idle technician hours, and skill mismatches. Ensures the most urgent condition-driven work gets the right technician at the right time.</t>
   </si>
   <si>
@@ -744,9 +720,6 @@
     <t>PM Lifecycle Optimized</t>
   </si>
   <si>
-    <t>Preventive maintenance intervals adjusted using condition data and health signals. Over-maintained assets de-escalated; under-maintained assets identified before failure.</t>
-  </si>
-  <si>
     <t>Reduces unnecessary planned downtime and maintenance labor cost.</t>
   </si>
   <si>
@@ -789,9 +762,6 @@
   </si>
   <si>
     <t>Planning Dashboard</t>
-  </si>
-  <si>
-    <t>Planning Dashboard in Maximo live with cost, resource, and compliance views populated from real data. Three KPI views: cost (labor/materials/tools/services); resource (demand vs available hours); compliance (planned vs actual).</t>
   </si>
   <si>
     <t>Makes planned-vs-actual analysis automatic and accessible. Replaces manual Power BI exports.</t>
@@ -840,9 +810,6 @@
     <t>Job Plans — AIP Connection</t>
   </si>
   <si>
-    <t>Asset Investment Planning (AIP) outputs begin to connect to job plan definitions. Job plans leverage asset condition data as inputs.</t>
-  </si>
-  <si>
     <t>Asset-specific maintenance planning driven by lifecycle data.</t>
   </si>
   <si>
@@ -885,9 +852,6 @@
   </si>
   <si>
     <t>GenAI Prescriptive Recommendations</t>
-  </si>
-  <si>
-    <t>AI-driven prescriptive recommendations active across all critical asset classes: what to do, when, with which parts, and in what sequence.</t>
   </si>
   <si>
     <t>Scales reliability expertise to every technician and engineer at the point of work.</t>
@@ -3838,6 +3802,42 @@
   <si>
     <t xml:space="preserve">Reliability becomes a compounding, self-improving system instead of a set of one-time projects. FMEA is reviewed on a continuous cycle, refined by real RSE evidence rather than reopened once and forgotten. Inventory strategy shifts from stocking against fear to stocking against actual predicted risk. And the loop closes all the way back to procurement — every failure investigated in operations informs the next asset you buy, so reliability gets designed in before an asset ever enters service, not fixed after the fact. This is the difference between managing failures and preventing them.
 </t>
+  </si>
+  <si>
+    <t>A trusted, governed asset registry in Maximo Manage with unique asset records, defined asset and location hierarchies, and standardized asset information. Serves as the single source of truth for critical maintenance assets.</t>
+  </si>
+  <si>
+    <t>The organization's most critical assets are classified by criticality tier (Critical / High / Medium / Low) using a repeatable scoring methodology that is consistently applied across at least one critical asset class.</t>
+  </si>
+  <si>
+    <t>Parent-child asset hierarchies and location structures defined in Maximo to represent how critical equipment and systems are organized. Supports maintenance history analysis, cost visibility, asset rollups, and future condition and health monitoring initiatives.</t>
+  </si>
+  <si>
+    <t>Dependencies and relationships between assets, locations, and systems modeled in Maximo to reflect how equipment operates together. Supports system-level maintenance planning, outage and shutdown planning.</t>
+  </si>
+  <si>
+    <t>Job plans exist in Maximo as reusable work templates linked to work orders and preventive maintenance records. Each job plan includes estimated duration and defined labor, craft, or crew requirements to support consistent work execution.</t>
+  </si>
+  <si>
+    <t>Job plans enriched with labor, materials, tools, services, work type classifications, and asset-specific requirements to support consistent planning, scheduling, and execution of maintenance work.</t>
+  </si>
+  <si>
+    <t>Job plans are structured to reflect complex maintenance activities, with related job plans generating parent-child work order hierarchies. Job plans are associated with specific asset classifications to support standardized maintenance practices across similar assets.</t>
+  </si>
+  <si>
+    <t>Technician scheduling and dispatch optimized using work priority, job urgency, required skills, location, and workforce availability. Crew assignments are matched to work requirements to improve schedule efficiency, workforce utilization, and timely completion of maintenance activities. When condition-based maintenance is used, asset condition information can also be considered to help prioritize and schedule work.</t>
+  </si>
+  <si>
+    <t>Preventive maintenance intervals are adjusted using asset condition and health signals. Maintenance plans and work volumes are optimized to reduce unnecessary work, prioritize emerging risks, and improve asset reliability while making more effective use of field resources.</t>
+  </si>
+  <si>
+    <t>A planning dashboard in Maximo provides real-time visibility into maintenance cost, resource capacity, and compliance performance using operational data. Planning decisions are guided by three KPI views: cost (labor, materials, tools, and services), resource (forecast demand versus available workforce capacity), and compliance (planned versus actual work execution). This enables proactive planning, improved resource allocation, and greater control of maintenance performance.</t>
+  </si>
+  <si>
+    <t>Asset Investment Planning (AIP) outputs are integrated with job plan definitions. Job plans use asset condition, health, and risk data to drive maintenance decisions, aligning work execution with asset lifecycle and investment priorities.</t>
+  </si>
+  <si>
+    <t>AI-driven prescriptive recommendations guide maintenance decisions across all critical asset classes, recommending what work to perform, when to perform it, which parts and resources are required, and the optimal execution sequence.</t>
   </si>
 </sst>
 </file>
@@ -5092,42 +5092,42 @@
         <v>106</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H2" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="I2" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="J2" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="L2" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="L2" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="P2" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="Q2" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
@@ -5136,210 +5136,210 @@
         <v>103</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E3" s="31" t="s">
         <v>105</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H3" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="J3" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="I3" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="K3" s="20" t="s">
         <v>102</v>
       </c>
       <c r="L3" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="O3" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="P3" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="O3" s="14" t="s">
+      <c r="Q3" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="P3" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q3" s="14" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="31" t="s">
+      <c r="G4" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="H4" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="J4" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="K4" s="20" t="s">
         <v>102</v>
       </c>
       <c r="L4" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="O4" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="P4" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="O4" s="14" t="s">
+      <c r="Q4" s="14" t="s">
         <v>141</v>
-      </c>
-      <c r="P4" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q4" s="14" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D5" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="G5" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="I5" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="I5" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="K5" s="20" t="s">
         <v>102</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M5" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="P5" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="Q5" s="14" t="s">
         <v>153</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q5" s="14" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="I6" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="K6" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="N6" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="I6" s="33" t="s">
+      <c r="O6" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="P6" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="K6" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="M6" s="4" t="s">
+      <c r="Q6" s="14" t="s">
         <v>164</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="O6" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="P6" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q6" s="14" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>6</v>
@@ -5351,419 +5351,419 @@
         <v>104</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="I7" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="M7" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="N7" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="O7" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="I7" s="33" t="s">
+      <c r="P7" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="Q7" s="14" t="s">
         <v>174</v>
-      </c>
-      <c r="K7" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="L7" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="O7" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="P7" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q7" s="14" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="N8" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="O8" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="H8" s="33" t="s">
+      <c r="P8" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="I8" s="33" t="s">
+      <c r="Q8" s="14" t="s">
         <v>184</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="K8" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="O8" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="P8" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q8" s="14" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="N9" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="O9" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="H9" s="33" t="s">
+      <c r="P9" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="I9" s="33" t="s">
+      <c r="Q9" s="14" t="s">
         <v>195</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="K9" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="O9" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="P9" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q9" s="14" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="O10" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="P10" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="H10" s="33" t="s">
+      <c r="Q10" s="14" t="s">
         <v>206</v>
-      </c>
-      <c r="I10" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="K10" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="O10" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="P10" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q10" s="14" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="P11" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="Q11" s="14" t="s">
         <v>217</v>
-      </c>
-      <c r="H11" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="I11" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="K11" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="O11" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="P11" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q11" s="14" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="I12" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="O12" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="P12" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="E12" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="Q12" s="14" t="s">
         <v>230</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="H12" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="I12" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="K12" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="O12" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="P12" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q12" s="14" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D13" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="O13" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="P13" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="Q13" s="14" t="s">
         <v>243</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="H13" s="33" t="s">
-        <v>246</v>
-      </c>
-      <c r="I13" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="K13" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="P13" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q13" s="14" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="I14" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="O14" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q14" s="14" t="s">
         <v>256</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H14" s="33" t="s">
-        <v>260</v>
-      </c>
-      <c r="I14" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="K14" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="O14" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="P14" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q14" s="14" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
@@ -5775,207 +5775,207 @@
         <v>104</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="H15" s="33" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="I15" s="33" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="O15" s="14" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="H16" s="33" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="I16" s="33" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="N16" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="O16" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="O16" s="14" t="s">
-        <v>288</v>
-      </c>
       <c r="P16" s="14" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="H17" s="33" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="I17" s="33" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="O17" s="14" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="H18" s="33" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="I18" s="33" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="K18" s="20" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="O18" s="14" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="P18" s="14" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>18</v>
@@ -5987,260 +5987,260 @@
         <v>104</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="H19" s="33" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="I19" s="33" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="O19" s="14" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="P19" s="14" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="H20" s="33" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="I20" s="33" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="K20" s="20" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="P20" s="14" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="H21" s="33" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="I21" s="33" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="N21" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="O21" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="O21" s="14" t="s">
-        <v>345</v>
-      </c>
       <c r="P21" s="14" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="H22" s="33" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="I22" s="33" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="K22" s="20" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="O22" s="14" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="P22" s="14" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="H23" s="33" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="I23" s="33" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="P23" s="14" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>21</v>
@@ -6252,260 +6252,260 @@
         <v>104</v>
       </c>
       <c r="E24" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="H24" s="33" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="I24" s="33" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="K24" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="O24" s="14" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="P24" s="14" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="Q24" s="14" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="H25" s="33" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="I25" s="33" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="K25" s="20" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="O25" s="14" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="P25" s="14" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="H26" s="33" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="I26" s="33" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="K26" s="20" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="O26" s="14" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="P26" s="14" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="H27" s="33" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="I27" s="33" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="K27" s="20" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="O27" s="14" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="P27" s="14" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E28" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="H28" s="33" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="I28" s="33" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="K28" s="20" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="O28" s="14" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="P28" s="14" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="Q28" s="14" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>24</v>
@@ -6517,154 +6517,154 @@
         <v>104</v>
       </c>
       <c r="E29" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="H29" s="33" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="I29" s="33" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="K29" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L29" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="O29" s="14" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="P29" s="14" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E30" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="H30" s="33" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="I30" s="33" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="K30" s="20" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="O30" s="14" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="P30" s="14" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E31" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="H31" s="33" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="I31" s="33" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="K31" s="20" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="O31" s="14" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="P31" s="14" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>27</v>
@@ -6673,475 +6673,475 @@
         <v>103</v>
       </c>
       <c r="D32" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E32" s="31" t="s">
         <v>105</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="H32" s="33" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="I32" s="33" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="K32" s="20" t="s">
         <v>102</v>
       </c>
       <c r="L32" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="O32" s="14" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="P32" s="14" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="H33" s="33" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="I33" s="33" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="K33" s="20" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="L33" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="N33" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="O33" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="O33" s="14" t="s">
-        <v>483</v>
-      </c>
       <c r="P33" s="14" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="H34" s="33" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="I34" s="33" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="K34" s="20" t="s">
         <v>102</v>
       </c>
       <c r="L34" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="O34" s="14" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="P34" s="14" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="B35" t="s">
         <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F35" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="G35" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="H35" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="I35" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="J35" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="K35" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="L35" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M35" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="N35" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="O35" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="P35" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="Q35" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="H36" s="33" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I36" s="33" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="K36" s="20" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="O36" s="14" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="P36" s="14" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="H37" s="33" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="I37" s="33" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="K37" s="20" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="O37" s="14" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="P37" s="14" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="H38" s="33" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="I38" s="33" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="K38" s="20" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="L38" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="O38" s="14" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="H39" s="33" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="I39" s="33" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="K39" s="20" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="L39" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="O39" s="14" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="P39" s="14" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="H40" s="33" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="I40" s="33" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="K40" s="20" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="L40" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="O40" s="14" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="P40" s="14" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>30</v>
@@ -7150,263 +7150,263 @@
         <v>103</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E41" s="31" t="s">
         <v>105</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="H41" s="33" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="I41" s="33" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="K41" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L41" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="O41" s="14" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="P41" s="14" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>30</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="H42" s="33" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="I42" s="33" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="K42" s="20" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="L42" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="O42" s="14" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="P42" s="14" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>30</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D43" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="H43" s="33" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="I43" s="33" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="K43" s="20" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="L43" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M43" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="O43" s="14" t="s">
         <v>587</v>
       </c>
-      <c r="N43" s="4" t="s">
+      <c r="P43" s="14" t="s">
         <v>588</v>
       </c>
-      <c r="O43" s="14" t="s">
-        <v>599</v>
-      </c>
-      <c r="P43" s="14" t="s">
-        <v>600</v>
-      </c>
       <c r="Q43" s="14" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="H44" s="33" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="I44" s="33" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="K44" s="20" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="L44" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="O44" s="14" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="P44" s="14" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="Q44" s="14" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>30</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="H45" s="33" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="I45" s="33" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="K45" s="20" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="L45" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="O45" s="14" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="P45" s="14" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>12</v>
@@ -7418,366 +7418,366 @@
         <v>104</v>
       </c>
       <c r="E46" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="H46" s="33" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="I46" s="33" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="K46" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L46" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="O46" s="14" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="P46" s="14" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="Q46" s="14" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E47" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="H47" s="33" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="I47" s="33" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="K47" s="20" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="L47" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="N47" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="O47" s="14" t="s">
+        <v>630</v>
+      </c>
+      <c r="P47" s="14" t="s">
         <v>631</v>
       </c>
-      <c r="O47" s="14" t="s">
-        <v>642</v>
-      </c>
-      <c r="P47" s="14" t="s">
-        <v>643</v>
-      </c>
       <c r="Q47" s="14" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E48" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="H48" s="33" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="I48" s="33" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="K48" s="20" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="L48" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="O48" s="14" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="P48" s="14" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="Q48" s="14" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E49" s="31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="H49" s="33" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="I49" s="33" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="K49" s="20" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="L49" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="O49" s="14" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="P49" s="14" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E50" s="31" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="H50" s="33" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="I50" s="33" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="K50" s="20" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="L50" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="O50" s="14" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="P50" s="14" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="Q50" s="14" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E51" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="H51" s="33" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="I51" s="33" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="K51" s="20" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="L51" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="O51" s="14" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="P51" s="14" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="Q51" s="14" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
     </row>
     <row r="52" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E52" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="H52" s="33" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="I52" s="33" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="K52" s="20" t="s">
         <v>102</v>
       </c>
       <c r="L52" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="O52" s="14" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="P52" s="14" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="Q52" s="14" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
     </row>
     <row r="53" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>33</v>
@@ -7786,499 +7786,499 @@
         <v>103</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>704</v>
+        <v>692</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="H53" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="I53" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="J53" s="14" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="K53" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L53" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M53" s="14" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="N53" s="14" t="s">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="O53" s="14" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="P53" s="14" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="Q53" s="14" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>104</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="H54" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="I54" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="K54" s="14" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="L54" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M54" s="14" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="N54" s="14" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="O54" s="14" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="P54" s="14" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="Q54" s="14" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="I55" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="J55" s="14" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="K55" s="14" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="L55" s="14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M55" s="14" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="N55" s="14" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="O55" s="14" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="P55" s="14" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="Q55" s="14" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="I56" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="K56" s="14" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="L56" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M56" s="14" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="N56" s="14" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="O56" s="14" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="P56" s="14" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="Q56" s="14" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="G57" s="14" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
       <c r="I57" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="J57" s="14" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="K57" s="14" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
       <c r="L57" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M57" s="14" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="N57" s="14" t="s">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="O57" s="14" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="P57" s="14" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="Q57" s="14" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="I58" t="s">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="K58" s="14" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="L58" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M58" s="14" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="N58" s="14" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="O58" s="14" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="P58" s="14" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="Q58" s="14" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="I59" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="K59" s="14" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="L59" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M59" s="14" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="N59" s="14" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="O59" s="14" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="P59" s="14" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="I60" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="K60" s="14" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="L60" s="14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M60" s="14" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="N60" s="14" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="O60" s="14" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="P60" s="14" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="Q60" s="14" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="14" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="I61" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="J61" s="14" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="K61" s="14" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="L61" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M61" s="14" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="N61" s="14" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="O61" s="14" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="P61" s="14" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="165" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>36</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>805</v>
+        <v>793</v>
       </c>
       <c r="I62" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="K62" s="14" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="L62" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M62" s="14" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="N62" s="14" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="O62" s="14" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="P62" s="14" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="Q62" s="14" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -8304,13 +8304,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>816</v>
+        <v>804</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -8321,10 +8321,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>817</v>
+        <v>805</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -8335,10 +8335,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>818</v>
+        <v>806</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -8349,1620 +8349,1620 @@
         <v>3</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B5" s="35">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B6" s="17">
         <v>2</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B7" s="38">
         <v>3</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B8" s="35">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B9" s="17">
         <v>2</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B10" s="38">
         <v>3</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B11" s="35">
         <v>1</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B12" s="17">
         <v>2</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B13" s="38">
         <v>3</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B14" s="35">
         <v>1</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B15" s="38">
         <v>2</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="B16" s="35">
         <v>1</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="B17" s="17">
         <v>2</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="B18" s="38">
         <v>3</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>840</v>
+        <v>828</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B19" s="35">
         <v>1</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>841</v>
+        <v>829</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B20" s="17">
         <v>2</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>842</v>
+        <v>830</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B21" s="38">
         <v>3</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>843</v>
+        <v>831</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B22" s="35">
         <v>1</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>844</v>
+        <v>832</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B23" s="17">
         <v>2</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>845</v>
+        <v>833</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="37" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B24" s="38">
         <v>3</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>846</v>
+        <v>834</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B25" s="35">
         <v>1</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="37" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B26" s="38">
         <v>2</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B27" s="35">
         <v>1</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>849</v>
+        <v>837</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B28" s="38">
         <v>2</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="34" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B29" s="35">
         <v>1</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="37" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B30" s="38">
         <v>2</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="D30" s="39" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="34" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B31" s="35">
         <v>1</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>856</v>
+        <v>844</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="37" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B32" s="38">
         <v>2</v>
       </c>
       <c r="C32" s="39" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="D32" s="39" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B33" s="35">
         <v>1</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="37" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B34" s="38">
         <v>2</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>861</v>
+        <v>849</v>
       </c>
       <c r="D34" s="39" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="34" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="B35" s="35">
         <v>1</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="37" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="B36" s="38">
         <v>2</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B37" s="35">
         <v>1</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="37" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B38" s="38">
         <v>2</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>840</v>
+        <v>828</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="34" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B39" s="35">
         <v>1</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
       <c r="D39" s="36" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B40" s="17">
         <v>2</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="37" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B41" s="38">
         <v>3</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="D41" s="39" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="34" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B42" s="35">
         <v>1</v>
       </c>
       <c r="C42" s="36" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
       <c r="D42" s="36" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="37" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B43" s="38">
         <v>2</v>
       </c>
       <c r="C43" s="39" t="s">
-        <v>875</v>
+        <v>863</v>
       </c>
       <c r="D43" s="39" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="34" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B44" s="35">
         <v>1</v>
       </c>
       <c r="C44" s="36" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B45" s="17">
         <v>2</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>878</v>
+        <v>866</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="37" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B46" s="38">
         <v>3</v>
       </c>
       <c r="C46" s="39" t="s">
-        <v>879</v>
+        <v>867</v>
       </c>
       <c r="D46" s="39" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="34" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="B47" s="35">
         <v>1</v>
       </c>
       <c r="C47" s="36" t="s">
-        <v>880</v>
+        <v>868</v>
       </c>
       <c r="D47" s="36" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="37" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="B48" s="38">
         <v>2</v>
       </c>
       <c r="C48" s="39" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="34" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="B49" s="35">
         <v>1</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>884</v>
+        <v>872</v>
       </c>
       <c r="D49" s="36" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="37" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="B50" s="38">
         <v>2</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="34" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="B51" s="35">
         <v>1</v>
       </c>
       <c r="C51" s="36" t="s">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="D51" s="36" t="s">
-        <v>887</v>
+        <v>875</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="37" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="B52" s="38">
         <v>2</v>
       </c>
       <c r="C52" s="39" t="s">
-        <v>888</v>
+        <v>876</v>
       </c>
       <c r="D52" s="39" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="34" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="B53" s="35">
         <v>1</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>889</v>
+        <v>877</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="37" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="B54" s="38">
         <v>2</v>
       </c>
       <c r="C54" s="39" t="s">
-        <v>890</v>
+        <v>878</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>891</v>
+        <v>879</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="34" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="B55" s="35">
         <v>1</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>892</v>
+        <v>880</v>
       </c>
       <c r="D55" s="36" t="s">
-        <v>893</v>
+        <v>881</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="37" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="B56" s="38">
         <v>2</v>
       </c>
       <c r="C56" s="39" t="s">
-        <v>894</v>
+        <v>882</v>
       </c>
       <c r="D56" s="39" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="34" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="B57" s="35">
         <v>1</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="D57" s="36" t="s">
-        <v>896</v>
+        <v>884</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="37" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="B58" s="38">
         <v>2</v>
       </c>
       <c r="C58" s="39" t="s">
-        <v>897</v>
+        <v>885</v>
       </c>
       <c r="D58" s="39" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="34" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="B59" s="35">
         <v>1</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>899</v>
+        <v>887</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>900</v>
+        <v>888</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="B60" s="17">
         <v>2</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>901</v>
+        <v>889</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="37" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="B61" s="38">
         <v>3</v>
       </c>
       <c r="C61" s="39" t="s">
-        <v>902</v>
+        <v>890</v>
       </c>
       <c r="D61" s="39" t="s">
-        <v>903</v>
+        <v>891</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="34" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="B62" s="35">
         <v>1</v>
       </c>
       <c r="C62" s="36" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
       <c r="D62" s="36" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="37" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="B63" s="38">
         <v>2</v>
       </c>
       <c r="C63" s="39" t="s">
-        <v>905</v>
+        <v>893</v>
       </c>
       <c r="D63" s="39" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="34" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="B64" s="35">
         <v>1</v>
       </c>
       <c r="C64" s="36" t="s">
-        <v>906</v>
+        <v>894</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="37" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="B65" s="38">
         <v>2</v>
       </c>
       <c r="C65" s="39" t="s">
-        <v>907</v>
+        <v>895</v>
       </c>
       <c r="D65" s="39" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="34" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B66" s="35">
         <v>1</v>
       </c>
       <c r="C66" s="36" t="s">
-        <v>908</v>
+        <v>896</v>
       </c>
       <c r="D66" s="36" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="37" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B67" s="38">
         <v>2</v>
       </c>
       <c r="C67" s="39" t="s">
-        <v>909</v>
+        <v>897</v>
       </c>
       <c r="D67" s="39" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="34" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="B68" s="35">
         <v>1</v>
       </c>
       <c r="C68" s="36" t="s">
-        <v>910</v>
+        <v>898</v>
       </c>
       <c r="D68" s="36" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="B69" s="17">
         <v>2</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>911</v>
+        <v>899</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>912</v>
+        <v>900</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="37" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="B70" s="38">
         <v>3</v>
       </c>
       <c r="C70" s="39" t="s">
-        <v>913</v>
+        <v>901</v>
       </c>
       <c r="D70" s="39" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="34" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B71" s="35">
         <v>1</v>
       </c>
       <c r="C71" s="36" t="s">
-        <v>914</v>
+        <v>902</v>
       </c>
       <c r="D71" s="36" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="37" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B72" s="38">
         <v>2</v>
       </c>
       <c r="C72" s="39" t="s">
-        <v>915</v>
+        <v>903</v>
       </c>
       <c r="D72" s="39" t="s">
-        <v>912</v>
+        <v>900</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="34" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B73" s="35">
         <v>1</v>
       </c>
       <c r="C73" s="36" t="s">
-        <v>916</v>
+        <v>904</v>
       </c>
       <c r="D73" s="36" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="37" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B74" s="38">
         <v>2</v>
       </c>
       <c r="C74" s="39" t="s">
-        <v>917</v>
+        <v>905</v>
       </c>
       <c r="D74" s="39" t="s">
-        <v>918</v>
+        <v>906</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="34" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B75" s="35">
         <v>1</v>
       </c>
       <c r="C75" s="36" t="s">
-        <v>919</v>
+        <v>907</v>
       </c>
       <c r="D75" s="36" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="37" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B76" s="38">
         <v>2</v>
       </c>
       <c r="C76" s="39" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="D76" s="39" t="s">
-        <v>922</v>
+        <v>910</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="34" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="B77" s="35">
         <v>1</v>
       </c>
       <c r="C77" s="36" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="D77" s="36" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="37" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="B78" s="38">
         <v>2</v>
       </c>
       <c r="C78" s="39" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="D78" s="39" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="34" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="B79" s="35">
         <v>1</v>
       </c>
       <c r="C79" s="36" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="D79" s="36" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="37" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="B80" s="38">
         <v>2</v>
       </c>
       <c r="C80" s="39" t="s">
-        <v>927</v>
+        <v>915</v>
       </c>
       <c r="D80" s="39" t="s">
-        <v>928</v>
+        <v>916</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="34" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B81" s="35">
         <v>1</v>
       </c>
       <c r="C81" s="36" t="s">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="D81" s="36" t="s">
-        <v>930</v>
+        <v>918</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="37" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B82" s="38">
         <v>2</v>
       </c>
       <c r="C82" s="39" t="s">
-        <v>931</v>
+        <v>919</v>
       </c>
       <c r="D82" s="39" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="34" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B83" s="35">
         <v>1</v>
       </c>
       <c r="C83" s="36" t="s">
-        <v>932</v>
+        <v>920</v>
       </c>
       <c r="D83" s="36" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B84" s="17">
         <v>2</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>933</v>
+        <v>921</v>
       </c>
       <c r="D84" s="18" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="37" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B85" s="38">
         <v>3</v>
       </c>
       <c r="C85" s="39" t="s">
-        <v>934</v>
+        <v>922</v>
       </c>
       <c r="D85" s="39" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="34" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="B86" s="35">
         <v>1</v>
       </c>
       <c r="C86" s="36" t="s">
-        <v>935</v>
+        <v>923</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="37" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="B87" s="38">
         <v>2</v>
       </c>
       <c r="C87" s="39" t="s">
-        <v>936</v>
+        <v>924</v>
       </c>
       <c r="D87" s="39" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="40" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="B88" s="41">
         <v>1</v>
       </c>
       <c r="C88" s="42" t="s">
-        <v>937</v>
+        <v>925</v>
       </c>
       <c r="D88" s="42" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="B89" s="43">
         <v>2</v>
       </c>
       <c r="C89" s="44" t="s">
-        <v>939</v>
+        <v>927</v>
       </c>
       <c r="D89" s="44" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="45" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="B90" s="46">
         <v>3</v>
       </c>
       <c r="C90" s="47" t="s">
-        <v>940</v>
+        <v>928</v>
       </c>
       <c r="D90" s="47" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="34" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B91" s="35">
         <v>1</v>
       </c>
       <c r="C91" s="36" t="s">
-        <v>941</v>
+        <v>929</v>
       </c>
       <c r="D91" s="36" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B92" s="17">
         <v>2</v>
       </c>
       <c r="C92" s="18" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="D92" s="18" t="s">
-        <v>943</v>
+        <v>931</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="37" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B93" s="38">
         <v>3</v>
       </c>
       <c r="C93" s="39" t="s">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="D93" s="39" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94" t="s">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="D94" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="B95">
         <v>2</v>
       </c>
       <c r="C95" t="s">
-        <v>946</v>
+        <v>934</v>
       </c>
       <c r="D95" t="s">
-        <v>918</v>
+        <v>906</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="34" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="B96" s="35">
         <v>1</v>
       </c>
       <c r="C96" s="36" t="s">
-        <v>947</v>
+        <v>935</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="37" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="B97" s="38">
         <v>2</v>
       </c>
       <c r="C97" s="39" t="s">
-        <v>948</v>
+        <v>936</v>
       </c>
       <c r="D97" s="39" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="34" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="B98" s="35">
         <v>1</v>
       </c>
       <c r="C98" s="36" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="37" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="B99" s="38">
         <v>2</v>
       </c>
       <c r="C99" s="39" t="s">
-        <v>950</v>
+        <v>938</v>
       </c>
       <c r="D99" s="39" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="34" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="B100" s="35">
         <v>1</v>
       </c>
       <c r="C100" s="36" t="s">
-        <v>951</v>
+        <v>939</v>
       </c>
       <c r="D100" s="36" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="37" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="B101" s="38">
         <v>2</v>
       </c>
       <c r="C101" s="39" t="s">
-        <v>952</v>
+        <v>940</v>
       </c>
       <c r="D101" s="39" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="34" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="B102" s="35">
         <v>1</v>
       </c>
       <c r="C102" s="36" t="s">
-        <v>953</v>
+        <v>941</v>
       </c>
       <c r="D102" s="36" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="37" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="B103" s="38">
         <v>2</v>
       </c>
       <c r="C103" s="39" t="s">
-        <v>954</v>
+        <v>942</v>
       </c>
       <c r="D103" s="39" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="34" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="B104" s="35">
         <v>1</v>
       </c>
       <c r="C104" s="36" t="s">
-        <v>955</v>
+        <v>943</v>
       </c>
       <c r="D104" s="36" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="37" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="B105" s="38">
         <v>2</v>
       </c>
       <c r="C105" s="39" t="s">
-        <v>957</v>
+        <v>945</v>
       </c>
       <c r="D105" s="39" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="34" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="B106" s="35">
         <v>1</v>
       </c>
       <c r="C106" s="36" t="s">
-        <v>958</v>
+        <v>946</v>
       </c>
       <c r="D106" s="36" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="37" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="B107" s="38">
         <v>2</v>
       </c>
       <c r="C107" s="39" t="s">
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="D107" s="39" t="s">
-        <v>961</v>
+        <v>949</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="34" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="B108" s="35">
         <v>1</v>
       </c>
       <c r="C108" s="36" t="s">
-        <v>962</v>
+        <v>950</v>
       </c>
       <c r="D108" s="36" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="37" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="B109" s="38">
         <v>2</v>
       </c>
       <c r="C109" s="39" t="s">
-        <v>963</v>
+        <v>951</v>
       </c>
       <c r="D109" s="39" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="34" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="B110" s="35">
         <v>1</v>
       </c>
       <c r="C110" s="36" t="s">
-        <v>964</v>
+        <v>952</v>
       </c>
       <c r="D110" s="36" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="37" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="B111" s="38">
         <v>2</v>
       </c>
       <c r="C111" s="39" t="s">
-        <v>965</v>
+        <v>953</v>
       </c>
       <c r="D111" s="39" t="s">
-        <v>966</v>
+        <v>954</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="34" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="B112" s="35">
         <v>1</v>
       </c>
       <c r="C112" s="36" t="s">
-        <v>967</v>
+        <v>955</v>
       </c>
       <c r="D112" s="36" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="37" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="B113" s="38">
         <v>2</v>
       </c>
       <c r="C113" s="39" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="D113" s="39" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="34" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="B114" s="35">
         <v>1</v>
       </c>
       <c r="C114" s="36" t="s">
-        <v>969</v>
+        <v>957</v>
       </c>
       <c r="D114" s="36" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="37" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="B115" s="38">
         <v>2</v>
       </c>
       <c r="C115" s="39" t="s">
-        <v>970</v>
+        <v>958</v>
       </c>
       <c r="D115" s="39" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="34" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="B116" s="35">
         <v>1</v>
       </c>
       <c r="C116" s="36" t="s">
-        <v>971</v>
+        <v>959</v>
       </c>
       <c r="D116" s="36" t="s">
-        <v>961</v>
+        <v>949</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="37" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="B117" s="38">
         <v>2</v>
       </c>
       <c r="C117" s="39" t="s">
-        <v>972</v>
+        <v>960</v>
       </c>
       <c r="D117" s="39" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="34" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="B118" s="35">
         <v>1</v>
       </c>
       <c r="C118" s="36" t="s">
-        <v>973</v>
+        <v>961</v>
       </c>
       <c r="D118" s="36" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="16" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="B119" s="17">
         <v>2</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>974</v>
+        <v>962</v>
       </c>
       <c r="D119" s="18" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -9986,13 +9986,13 @@
   <sheetData>
     <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>976</v>
+        <v>964</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>977</v>
+        <v>965</v>
       </c>
       <c r="D1" s="25" t="s">
         <v>60</v>
@@ -10001,10 +10001,10 @@
         <v>63</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>979</v>
+        <v>967</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
@@ -10012,114 +10012,114 @@
         <v>104</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>980</v>
+        <v>968</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>981</v>
+        <v>969</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>982</v>
+        <v>970</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>983</v>
+        <v>971</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>984</v>
+        <v>972</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>985</v>
+        <v>973</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="111.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>988</v>
+        <v>976</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>989</v>
+        <v>977</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>990</v>
+        <v>978</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>991</v>
+        <v>979</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>992</v>
+        <v>980</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>993</v>
+        <v>981</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>994</v>
+        <v>982</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>995</v>
+        <v>983</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>996</v>
+        <v>984</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>997</v>
+        <v>985</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>998</v>
+        <v>986</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>999</v>
+        <v>987</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1000</v>
+        <v>988</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>1001</v>
+        <v>989</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>1002</v>
+        <v>990</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>1003</v>
+        <v>991</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>1004</v>
+        <v>992</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>1005</v>
+        <v>993</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>1006</v>
+        <v>994</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>1009</v>
+        <v>997</v>
       </c>
     </row>
   </sheetData>
@@ -10143,13 +10143,13 @@
   <sheetData>
     <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>976</v>
+        <v>964</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>977</v>
+        <v>965</v>
       </c>
       <c r="D1" s="25" t="s">
         <v>60</v>
@@ -10158,10 +10158,10 @@
         <v>63</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>979</v>
+        <v>967</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="111.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10169,114 +10169,114 @@
         <v>105</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>980</v>
+        <v>968</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>1107</v>
+        <v>1095</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>1108</v>
+        <v>1096</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>1011</v>
+        <v>999</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>1012</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>1109</v>
+        <v>1097</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>1110</v>
+        <v>1098</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>1015</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>992</v>
+        <v>980</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>1016</v>
+        <v>1004</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>998</v>
+        <v>986</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>1018</v>
+        <v>1006</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>1004</v>
+        <v>992</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>1117</v>
+        <v>1105</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>1119</v>
+        <v>1107</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>1020</v>
+        <v>1008</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>1021</v>
+        <v>1009</v>
       </c>
     </row>
   </sheetData>
@@ -10741,16 +10741,16 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="71" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
       <c r="B1" s="71" t="s">
-        <v>1023</v>
+        <v>1011</v>
       </c>
       <c r="C1" s="49"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
-        <v>1024</v>
+        <v>1012</v>
       </c>
       <c r="B2" s="72">
         <v>61</v>
@@ -10764,10 +10764,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="48" t="s">
-        <v>1025</v>
+        <v>1013</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>1026</v>
+        <v>1014</v>
       </c>
       <c r="C4" s="49"/>
     </row>
@@ -10886,16 +10886,16 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="48" t="s">
-        <v>1027</v>
+        <v>1015</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>1023</v>
+        <v>1011</v>
       </c>
       <c r="C18" s="49"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="76" t="s">
-        <v>1028</v>
+        <v>1016</v>
       </c>
       <c r="B19" s="74">
         <v>17</v>
@@ -10904,7 +10904,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="86" t="s">
-        <v>1029</v>
+        <v>1017</v>
       </c>
       <c r="B20" s="74">
         <v>29</v>
@@ -10913,7 +10913,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="73" t="s">
-        <v>1030</v>
+        <v>1018</v>
       </c>
       <c r="B21" s="74">
         <v>14</v>
@@ -10922,7 +10922,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="85" t="s">
-        <v>1031</v>
+        <v>1019</v>
       </c>
       <c r="B22" s="74">
         <v>1</v>
@@ -10936,16 +10936,16 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="48" t="s">
-        <v>1032</v>
+        <v>1020</v>
       </c>
       <c r="B24" s="71" t="s">
-        <v>1033</v>
+        <v>1021</v>
       </c>
       <c r="C24" s="49"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="49" t="s">
-        <v>1034</v>
+        <v>1022</v>
       </c>
       <c r="B25" s="74">
         <v>8</v>
@@ -10954,7 +10954,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="49" t="s">
-        <v>1035</v>
+        <v>1023</v>
       </c>
       <c r="B26" s="74">
         <v>11</v>
@@ -10963,7 +10963,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="49" t="s">
-        <v>1036</v>
+        <v>1024</v>
       </c>
       <c r="B27" s="74">
         <v>13</v>
@@ -10972,7 +10972,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="49" t="s">
-        <v>1037</v>
+        <v>1025</v>
       </c>
       <c r="B28" s="74">
         <v>8</v>
@@ -10981,7 +10981,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="49" t="s">
-        <v>1038</v>
+        <v>1026</v>
       </c>
       <c r="B29" s="74">
         <v>6</v>
@@ -10990,7 +10990,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="49" t="s">
-        <v>1039</v>
+        <v>1027</v>
       </c>
       <c r="B30" s="74">
         <v>4</v>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="49" t="s">
-        <v>1040</v>
+        <v>1028</v>
       </c>
       <c r="B31" s="74">
         <v>6</v>
@@ -11008,7 +11008,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="49" t="s">
-        <v>1041</v>
+        <v>1029</v>
       </c>
       <c r="B32" s="74">
         <v>10</v>
@@ -11017,7 +11017,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="49" t="s">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="B33" s="74">
         <v>7</v>
@@ -11026,7 +11026,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="49" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="B34" s="74">
         <v>4</v>
@@ -11081,226 +11081,226 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="87" t="s">
-        <v>1044</v>
+        <v>1032</v>
       </c>
       <c r="B1" s="87" t="s">
-        <v>1045</v>
+        <v>1033</v>
       </c>
       <c r="C1" s="87" t="s">
-        <v>1046</v>
+        <v>1034</v>
       </c>
       <c r="D1" s="87" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
       <c r="E1" s="87" t="s">
-        <v>1048</v>
+        <v>1036</v>
       </c>
       <c r="F1" s="87" t="s">
-        <v>1049</v>
+        <v>1037</v>
       </c>
       <c r="G1" s="87" t="s">
-        <v>1050</v>
+        <v>1038</v>
       </c>
       <c r="H1" s="87" t="s">
-        <v>1051</v>
+        <v>1039</v>
       </c>
       <c r="I1" s="87" t="s">
-        <v>1052</v>
+        <v>1040</v>
       </c>
       <c r="J1" s="87" t="s">
-        <v>1053</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="88" t="s">
-        <v>1054</v>
+        <v>1042</v>
       </c>
       <c r="B2" s="89" t="s">
-        <v>1055</v>
+        <v>1043</v>
       </c>
       <c r="C2" s="90" t="s">
-        <v>1056</v>
+        <v>1044</v>
       </c>
       <c r="D2" s="89" t="s">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="E2" s="91" t="s">
-        <v>1058</v>
+        <v>1046</v>
       </c>
       <c r="F2" s="91" t="s">
-        <v>1059</v>
+        <v>1047</v>
       </c>
       <c r="G2" s="91" t="s">
-        <v>1060</v>
+        <v>1048</v>
       </c>
       <c r="H2" s="91" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
       <c r="I2" s="91" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="J2" s="91" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="88" t="s">
-        <v>1064</v>
+        <v>1052</v>
       </c>
       <c r="B3" s="89" t="s">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="C3" s="92" t="s">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="D3" s="89" t="s">
-        <v>1067</v>
+        <v>1055</v>
       </c>
       <c r="E3" s="91" t="s">
-        <v>1068</v>
+        <v>1056</v>
       </c>
       <c r="F3" s="91" t="s">
-        <v>1069</v>
+        <v>1057</v>
       </c>
       <c r="G3" s="91" t="s">
-        <v>1070</v>
+        <v>1058</v>
       </c>
       <c r="H3" s="91" t="s">
-        <v>1071</v>
+        <v>1059</v>
       </c>
       <c r="I3" s="91" t="s">
-        <v>1072</v>
+        <v>1060</v>
       </c>
       <c r="J3" s="91" t="s">
-        <v>1073</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="88" t="s">
-        <v>1074</v>
+        <v>1062</v>
       </c>
       <c r="B4" s="89" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C4" s="92" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D4" s="89" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E4" s="91" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F4" s="91" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G4" s="91" t="s">
         <v>1065</v>
       </c>
-      <c r="C4" s="92" t="s">
+      <c r="H4" s="91" t="s">
         <v>1066</v>
       </c>
-      <c r="D4" s="89" t="s">
+      <c r="I4" s="91" t="s">
         <v>1067</v>
       </c>
-      <c r="E4" s="91" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F4" s="91" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G4" s="91" t="s">
-        <v>1077</v>
-      </c>
-      <c r="H4" s="91" t="s">
-        <v>1078</v>
-      </c>
-      <c r="I4" s="91" t="s">
-        <v>1079</v>
-      </c>
       <c r="J4" s="91" t="s">
-        <v>1080</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="88" t="s">
-        <v>1081</v>
+        <v>1069</v>
       </c>
       <c r="B5" s="89" t="s">
-        <v>1082</v>
+        <v>1070</v>
       </c>
       <c r="C5" s="92" t="s">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="D5" s="89" t="s">
-        <v>1067</v>
+        <v>1055</v>
       </c>
       <c r="E5" s="91" t="s">
-        <v>1083</v>
+        <v>1071</v>
       </c>
       <c r="F5" s="91" t="s">
-        <v>1084</v>
+        <v>1072</v>
       </c>
       <c r="G5" s="91" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="H5" s="91" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
       <c r="I5" s="91" t="s">
-        <v>1087</v>
+        <v>1075</v>
       </c>
       <c r="J5" s="91" t="s">
-        <v>1088</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="88" t="s">
-        <v>1089</v>
+        <v>1077</v>
       </c>
       <c r="B6" s="89" t="s">
-        <v>1090</v>
+        <v>1078</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="D6" s="89" t="s">
-        <v>1091</v>
+        <v>1079</v>
       </c>
       <c r="E6" s="91" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
       <c r="F6" s="91" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="G6" s="91" t="s">
-        <v>1094</v>
+        <v>1082</v>
       </c>
       <c r="H6" s="91" t="s">
-        <v>1095</v>
+        <v>1083</v>
       </c>
       <c r="I6" s="91" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
       <c r="J6" s="91" t="s">
-        <v>1097</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="88" t="s">
-        <v>1098</v>
+        <v>1086</v>
       </c>
       <c r="B7" s="89" t="s">
-        <v>1099</v>
+        <v>1087</v>
       </c>
       <c r="C7" s="93" t="s">
-        <v>1100</v>
+        <v>1088</v>
       </c>
       <c r="D7" s="89" t="s">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="E7" s="91" t="s">
-        <v>1101</v>
+        <v>1089</v>
       </c>
       <c r="F7" s="91" t="s">
-        <v>1102</v>
+        <v>1090</v>
       </c>
       <c r="G7" s="91" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="H7" s="91" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="I7" s="91" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="J7" s="91" t="s">
-        <v>1106</v>
+        <v>1094</v>
       </c>
     </row>
   </sheetData>

--- a/Logic/Milestone_Register_Sep20.xlsx
+++ b/Logic/Milestone_Register_Sep20.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EsterMonroyGatell\Documents\GitHub\M-GRAT\Logic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gosciminski/Documents/GitHub/M-GRAT/Logic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59615BF9-78D3-45F1-8C09-ECE6BD4C3F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B49F679-D30C-A643-B5F5-D4F4B9047D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4020" yWindow="660" windowWidth="29040" windowHeight="20960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="1121">
   <si>
     <t>Capability Pillar / Domain</t>
   </si>
@@ -1563,9 +1563,6 @@
     <t>CM-1-LF</t>
   </si>
   <si>
-    <t>Condition Monitoring — Low Frequency</t>
-  </si>
-  <si>
     <t>Collect asset condition data (meter readings, sensor values, inspection results) in Maximo Manage to trigger maintenance actions when predefined rules or thresholds are met.</t>
   </si>
   <si>
@@ -3838,6 +3835,12 @@
   </si>
   <si>
     <t>AI-driven prescriptive recommendations guide maintenance decisions across all critical asset classes, recommending what work to perform, when to perform it, which parts and resources are required, and the optimal execution sequence.</t>
+  </si>
+  <si>
+    <t>Condition Monitoring Triggers</t>
+  </si>
+  <si>
+    <t>Add ability to specify both hard and soft pre-requisites for a single milestone</t>
   </si>
 </sst>
 </file>
@@ -3898,37 +3901,44 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1C3557"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="41">
@@ -4152,7 +4162,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -4257,11 +4267,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4491,6 +4512,15 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="40" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="39" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4795,12 +4825,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="115" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="48" t="s">
         <v>92</v>
       </c>
@@ -4808,7 +4838,7 @@
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
         <v>93</v>
       </c>
@@ -4816,13 +4846,13 @@
       <c r="C2" s="49"/>
       <c r="D2" s="49"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="49"/>
       <c r="B3" s="49"/>
       <c r="C3" s="49"/>
       <c r="D3" s="49"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="51" t="s">
         <v>94</v>
       </c>
@@ -4830,7 +4860,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
     </row>
-    <row r="5" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A5" s="50" t="s">
         <v>95</v>
       </c>
@@ -4838,13 +4868,13 @@
       <c r="C5" s="49"/>
       <c r="D5" s="49"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="49"/>
       <c r="B6" s="49"/>
       <c r="C6" s="49"/>
       <c r="D6" s="49"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
         <v>96</v>
       </c>
@@ -4852,7 +4882,7 @@
       <c r="C7" s="49"/>
       <c r="D7" s="49"/>
     </row>
-    <row r="8" spans="1:4" ht="195" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="176" x14ac:dyDescent="0.2">
       <c r="A8" s="50" t="s">
         <v>97</v>
       </c>
@@ -4860,13 +4890,13 @@
       <c r="C8" s="49"/>
       <c r="D8" s="49"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="49"/>
       <c r="B9" s="49"/>
       <c r="C9" s="49"/>
       <c r="D9" s="49"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
         <v>98</v>
       </c>
@@ -4874,7 +4904,7 @@
       <c r="C10" s="49"/>
       <c r="D10" s="49"/>
     </row>
-    <row r="11" spans="1:4" ht="180" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="192" x14ac:dyDescent="0.2">
       <c r="A11" s="50" t="s">
         <v>99</v>
       </c>
@@ -4882,13 +4912,13 @@
       <c r="C11" s="49"/>
       <c r="D11" s="49"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="49"/>
       <c r="B12" s="49"/>
       <c r="C12" s="49"/>
       <c r="D12" s="49"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="51" t="s">
         <v>100</v>
       </c>
@@ -4896,7 +4926,7 @@
       <c r="C13" s="49"/>
       <c r="D13" s="49"/>
     </row>
-    <row r="14" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="80" x14ac:dyDescent="0.2">
       <c r="A14" s="50" t="s">
         <v>101</v>
       </c>
@@ -4904,91 +4934,91 @@
       <c r="C14" s="49"/>
       <c r="D14" s="49"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="49"/>
       <c r="B15" s="49"/>
       <c r="C15" s="49"/>
       <c r="D15" s="49"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="49"/>
       <c r="B16" s="49"/>
       <c r="C16" s="49"/>
       <c r="D16" s="49"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="49"/>
       <c r="B17" s="49"/>
       <c r="C17" s="49"/>
       <c r="D17" s="49"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="49"/>
       <c r="B18" s="49"/>
       <c r="C18" s="49"/>
       <c r="D18" s="49"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="49"/>
       <c r="B19" s="49"/>
       <c r="C19" s="49"/>
       <c r="D19" s="49"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="49"/>
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
       <c r="D20" s="49"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="49"/>
       <c r="B21" s="49"/>
       <c r="C21" s="49"/>
       <c r="D21" s="49"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="49"/>
       <c r="B22" s="49"/>
       <c r="C22" s="49"/>
       <c r="D22" s="49"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="49"/>
       <c r="B23" s="49"/>
       <c r="C23" s="49"/>
       <c r="D23" s="49"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="49"/>
       <c r="B24" s="49"/>
       <c r="C24" s="49"/>
       <c r="D24" s="49"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="49"/>
       <c r="B25" s="49"/>
       <c r="C25" s="49"/>
       <c r="D25" s="49"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="49"/>
       <c r="B26" s="49"/>
       <c r="C26" s="49"/>
       <c r="D26" s="49"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="49"/>
       <c r="B27" s="49"/>
       <c r="C27" s="49"/>
       <c r="D27" s="49"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="49"/>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="49"/>
       <c r="B29" s="49"/>
       <c r="C29" s="49"/>
@@ -5002,24 +5032,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q62"/>
-  <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="129" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.1640625" defaultRowHeight="129" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" customWidth="1"/>
+    <col min="4" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="73.42578125" customWidth="1"/>
-    <col min="11" max="12" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="49.28515625" customWidth="1"/>
-    <col min="14" max="14" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="73.5" customWidth="1"/>
+    <col min="11" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.33203125" customWidth="1"/>
+    <col min="14" max="14" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="64" style="14" customWidth="1"/>
     <col min="16" max="16" width="63" style="14" customWidth="1"/>
-    <col min="17" max="17" width="52.42578125" style="14" customWidth="1"/>
+    <col min="17" max="17" width="52.5" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -5072,7 +5102,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>102</v>
       </c>
@@ -5092,7 +5122,7 @@
         <v>106</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H2" s="33" t="s">
         <v>107</v>
@@ -5125,7 +5155,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>116</v>
       </c>
@@ -5145,7 +5175,7 @@
         <v>118</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>119</v>
@@ -5178,7 +5208,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>128</v>
       </c>
@@ -5231,7 +5261,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>142</v>
       </c>
@@ -5251,7 +5281,7 @@
         <v>145</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H5" s="33" t="s">
         <v>146</v>
@@ -5284,7 +5314,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>154</v>
       </c>
@@ -5304,7 +5334,7 @@
         <v>156</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H6" s="33" t="s">
         <v>157</v>
@@ -5337,7 +5367,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>165</v>
       </c>
@@ -5357,7 +5387,7 @@
         <v>166</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H7" s="33" t="s">
         <v>167</v>
@@ -5390,7 +5420,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>175</v>
       </c>
@@ -5410,7 +5440,7 @@
         <v>176</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>177</v>
@@ -5443,7 +5473,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>185</v>
       </c>
@@ -5463,7 +5493,7 @@
         <v>186</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>187</v>
@@ -5496,7 +5526,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>196</v>
       </c>
@@ -5516,7 +5546,7 @@
         <v>197</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>198</v>
@@ -5549,7 +5579,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>207</v>
       </c>
@@ -5569,7 +5599,7 @@
         <v>208</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H11" s="33" t="s">
         <v>209</v>
@@ -5602,7 +5632,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>218</v>
       </c>
@@ -5622,7 +5652,7 @@
         <v>221</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H12" s="33" t="s">
         <v>222</v>
@@ -5655,7 +5685,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>231</v>
       </c>
@@ -5675,7 +5705,7 @@
         <v>234</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H13" s="33" t="s">
         <v>235</v>
@@ -5708,7 +5738,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>244</v>
       </c>
@@ -5728,7 +5758,7 @@
         <v>247</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H14" s="33" t="s">
         <v>248</v>
@@ -5761,7 +5791,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>257</v>
       </c>
@@ -5814,7 +5844,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>268</v>
       </c>
@@ -5867,7 +5897,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>279</v>
       </c>
@@ -5920,7 +5950,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>291</v>
       </c>
@@ -5973,7 +6003,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>302</v>
       </c>
@@ -6026,7 +6056,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>313</v>
       </c>
@@ -6079,7 +6109,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>325</v>
       </c>
@@ -6132,7 +6162,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>336</v>
       </c>
@@ -6185,7 +6215,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>348</v>
       </c>
@@ -6238,7 +6268,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>359</v>
       </c>
@@ -6291,7 +6321,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>370</v>
       </c>
@@ -6344,7 +6374,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>382</v>
       </c>
@@ -6397,7 +6427,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>394</v>
       </c>
@@ -6450,7 +6480,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>406</v>
       </c>
@@ -6503,7 +6533,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>418</v>
       </c>
@@ -6556,7 +6586,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>429</v>
       </c>
@@ -6609,7 +6639,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>440</v>
       </c>
@@ -6662,7 +6692,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>452</v>
       </c>
@@ -6679,19 +6709,19 @@
         <v>105</v>
       </c>
       <c r="F32" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="H32" s="33" t="s">
         <v>454</v>
       </c>
-      <c r="H32" s="33" t="s">
+      <c r="I32" s="33" t="s">
         <v>455</v>
       </c>
-      <c r="I32" s="33" t="s">
+      <c r="J32" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>457</v>
       </c>
       <c r="K32" s="20" t="s">
         <v>102</v>
@@ -6700,24 +6730,24 @@
         <v>122</v>
       </c>
       <c r="M32" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="N32" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="N32" s="4" t="s">
+      <c r="O32" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="O32" s="14" t="s">
+      <c r="P32" s="14" t="s">
         <v>460</v>
       </c>
-      <c r="P32" s="14" t="s">
+      <c r="Q32" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="Q32" s="14" t="s">
+    </row>
+    <row r="33" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
         <v>462</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>27</v>
@@ -6732,45 +6762,45 @@
         <v>130</v>
       </c>
       <c r="F33" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="H33" s="33" t="s">
         <v>465</v>
       </c>
-      <c r="H33" s="33" t="s">
+      <c r="I33" s="33" t="s">
         <v>466</v>
       </c>
-      <c r="I33" s="33" t="s">
+      <c r="J33" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="J33" s="4" t="s">
+      <c r="K33" s="20" t="s">
         <v>468</v>
-      </c>
-      <c r="K33" s="20" t="s">
-        <v>469</v>
       </c>
       <c r="L33" s="21" t="s">
         <v>122</v>
       </c>
       <c r="M33" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="O33" s="14" t="s">
         <v>470</v>
       </c>
-      <c r="N33" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="O33" s="14" t="s">
+      <c r="P33" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="P33" s="14" t="s">
+      <c r="Q33" s="14" t="s">
         <v>472</v>
       </c>
-      <c r="Q33" s="14" t="s">
+    </row>
+    <row r="34" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
         <v>473</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>474</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>27</v>
@@ -6785,19 +6815,19 @@
         <v>130</v>
       </c>
       <c r="F34" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="H34" s="33" t="s">
         <v>476</v>
       </c>
-      <c r="H34" s="33" t="s">
+      <c r="I34" s="33" t="s">
         <v>477</v>
       </c>
-      <c r="I34" s="33" t="s">
+      <c r="J34" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>479</v>
       </c>
       <c r="K34" s="20" t="s">
         <v>102</v>
@@ -6806,24 +6836,24 @@
         <v>122</v>
       </c>
       <c r="M34" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="N34" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="N34" s="4" t="s">
+      <c r="O34" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="O34" s="14" t="s">
+      <c r="P34" s="14" t="s">
         <v>482</v>
       </c>
-      <c r="P34" s="14" t="s">
+      <c r="Q34" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="Q34" s="14" t="s">
+    </row>
+    <row r="35" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>484</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>485</v>
       </c>
       <c r="B35" t="s">
         <v>27</v>
@@ -6838,45 +6868,45 @@
         <v>144</v>
       </c>
       <c r="F35" t="s">
+        <v>485</v>
+      </c>
+      <c r="G35" t="s">
         <v>486</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>487</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>488</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>489</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>490</v>
-      </c>
-      <c r="K35" t="s">
-        <v>491</v>
       </c>
       <c r="L35" t="s">
         <v>122</v>
       </c>
       <c r="M35" t="s">
+        <v>491</v>
+      </c>
+      <c r="N35" t="s">
         <v>492</v>
       </c>
-      <c r="N35" t="s">
+      <c r="O35" t="s">
         <v>493</v>
       </c>
-      <c r="O35" t="s">
+      <c r="P35" t="s">
         <v>494</v>
       </c>
-      <c r="P35" t="s">
+      <c r="Q35" t="s">
         <v>495</v>
       </c>
-      <c r="Q35" t="s">
+    </row>
+    <row r="36" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
         <v>496</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>27</v>
@@ -6891,45 +6921,45 @@
         <v>144</v>
       </c>
       <c r="F36" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="H36" s="33" t="s">
         <v>499</v>
       </c>
-      <c r="H36" s="33" t="s">
+      <c r="I36" s="33" t="s">
         <v>500</v>
       </c>
-      <c r="I36" s="33" t="s">
+      <c r="J36" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="J36" s="4" t="s">
+      <c r="K36" s="20" t="s">
         <v>502</v>
-      </c>
-      <c r="K36" s="20" t="s">
-        <v>503</v>
       </c>
       <c r="L36" s="23" t="s">
         <v>136</v>
       </c>
       <c r="M36" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="O36" s="14" t="s">
         <v>504</v>
       </c>
-      <c r="N36" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="O36" s="14" t="s">
+      <c r="P36" s="14" t="s">
         <v>505</v>
       </c>
-      <c r="P36" s="14" t="s">
+      <c r="Q36" s="14" t="s">
         <v>506</v>
       </c>
-      <c r="Q36" s="14" t="s">
+    </row>
+    <row r="37" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
         <v>507</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>27</v>
@@ -6944,45 +6974,45 @@
         <v>144</v>
       </c>
       <c r="F37" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="H37" s="33" t="s">
         <v>510</v>
       </c>
-      <c r="H37" s="33" t="s">
+      <c r="I37" s="33" t="s">
         <v>511</v>
       </c>
-      <c r="I37" s="33" t="s">
+      <c r="J37" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="J37" s="4" t="s">
+      <c r="K37" s="20" t="s">
         <v>513</v>
-      </c>
-      <c r="K37" s="20" t="s">
-        <v>514</v>
       </c>
       <c r="L37" s="23" t="s">
         <v>136</v>
       </c>
       <c r="M37" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="N37" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="N37" s="4" t="s">
+      <c r="O37" s="14" t="s">
         <v>516</v>
       </c>
-      <c r="O37" s="14" t="s">
+      <c r="P37" s="14" t="s">
         <v>517</v>
       </c>
-      <c r="P37" s="14" t="s">
+      <c r="Q37" s="14" t="s">
         <v>518</v>
       </c>
-      <c r="Q37" s="14" t="s">
+    </row>
+    <row r="38" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
         <v>519</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>27</v>
@@ -6997,45 +7027,45 @@
         <v>233</v>
       </c>
       <c r="F38" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="H38" s="33" t="s">
         <v>522</v>
       </c>
-      <c r="H38" s="33" t="s">
+      <c r="I38" s="33" t="s">
         <v>523</v>
       </c>
-      <c r="I38" s="33" t="s">
+      <c r="J38" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="J38" s="4" t="s">
+      <c r="K38" s="20" t="s">
         <v>525</v>
-      </c>
-      <c r="K38" s="20" t="s">
-        <v>526</v>
       </c>
       <c r="L38" s="23" t="s">
         <v>136</v>
       </c>
       <c r="M38" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="N38" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="N38" s="4" t="s">
+      <c r="O38" s="14" t="s">
         <v>528</v>
       </c>
-      <c r="O38" s="14" t="s">
+      <c r="P38" s="14" t="s">
         <v>529</v>
       </c>
-      <c r="P38" s="14" t="s">
+      <c r="Q38" s="14" t="s">
         <v>530</v>
       </c>
-      <c r="Q38" s="14" t="s">
+    </row>
+    <row r="39" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
         <v>531</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>27</v>
@@ -7050,51 +7080,51 @@
         <v>233</v>
       </c>
       <c r="F39" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="H39" s="33" t="s">
         <v>534</v>
       </c>
-      <c r="H39" s="33" t="s">
+      <c r="I39" s="33" t="s">
         <v>535</v>
       </c>
-      <c r="I39" s="33" t="s">
+      <c r="J39" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="J39" s="4" t="s">
+      <c r="K39" s="20" t="s">
         <v>537</v>
-      </c>
-      <c r="K39" s="20" t="s">
-        <v>538</v>
       </c>
       <c r="L39" s="23" t="s">
         <v>136</v>
       </c>
       <c r="M39" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="N39" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="N39" s="4" t="s">
+      <c r="O39" s="14" t="s">
         <v>540</v>
       </c>
-      <c r="O39" s="14" t="s">
+      <c r="P39" s="14" t="s">
         <v>541</v>
       </c>
-      <c r="P39" s="14" t="s">
+      <c r="Q39" s="14" t="s">
         <v>542</v>
       </c>
-      <c r="Q39" s="14" t="s">
+    </row>
+    <row r="40" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
         <v>543</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D40" s="32" t="s">
         <v>110</v>
@@ -7103,45 +7133,45 @@
         <v>233</v>
       </c>
       <c r="F40" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="H40" s="33" t="s">
         <v>547</v>
       </c>
-      <c r="H40" s="33" t="s">
+      <c r="I40" s="33" t="s">
         <v>548</v>
       </c>
-      <c r="I40" s="33" t="s">
+      <c r="J40" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="J40" s="4" t="s">
+      <c r="K40" s="20" t="s">
         <v>550</v>
-      </c>
-      <c r="K40" s="20" t="s">
-        <v>551</v>
       </c>
       <c r="L40" s="22" t="s">
         <v>122</v>
       </c>
       <c r="M40" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="N40" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="N40" s="4" t="s">
+      <c r="O40" s="14" t="s">
         <v>553</v>
       </c>
-      <c r="O40" s="14" t="s">
+      <c r="P40" s="14" t="s">
         <v>554</v>
       </c>
-      <c r="P40" s="14" t="s">
+      <c r="Q40" s="14" t="s">
         <v>555</v>
       </c>
-      <c r="Q40" s="14" t="s">
+    </row>
+    <row r="41" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
         <v>556</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>30</v>
@@ -7156,19 +7186,19 @@
         <v>105</v>
       </c>
       <c r="F41" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="H41" s="33" t="s">
         <v>559</v>
       </c>
-      <c r="H41" s="33" t="s">
+      <c r="I41" s="33" t="s">
         <v>560</v>
       </c>
-      <c r="I41" s="33" t="s">
+      <c r="J41" s="4" t="s">
         <v>561</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>562</v>
       </c>
       <c r="K41" s="20" t="s">
         <v>110</v>
@@ -7177,24 +7207,24 @@
         <v>110</v>
       </c>
       <c r="M41" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="N41" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="N41" s="4" t="s">
+      <c r="O41" s="14" t="s">
         <v>564</v>
       </c>
-      <c r="O41" s="14" t="s">
+      <c r="P41" s="14" t="s">
         <v>565</v>
       </c>
-      <c r="P41" s="14" t="s">
+      <c r="Q41" s="14" t="s">
         <v>566</v>
       </c>
-      <c r="Q41" s="14" t="s">
+    </row>
+    <row r="42" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
         <v>567</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>568</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>30</v>
@@ -7209,45 +7239,45 @@
         <v>130</v>
       </c>
       <c r="F42" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="H42" s="33" t="s">
         <v>570</v>
       </c>
-      <c r="H42" s="33" t="s">
+      <c r="I42" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="I42" s="33" t="s">
+      <c r="J42" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="J42" s="4" t="s">
+      <c r="K42" s="20" t="s">
         <v>573</v>
-      </c>
-      <c r="K42" s="20" t="s">
-        <v>574</v>
       </c>
       <c r="L42" s="22" t="s">
         <v>122</v>
       </c>
       <c r="M42" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="N42" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="N42" s="4" t="s">
+      <c r="O42" s="14" t="s">
         <v>576</v>
       </c>
-      <c r="O42" s="14" t="s">
+      <c r="P42" s="14" t="s">
         <v>577</v>
       </c>
-      <c r="P42" s="14" t="s">
+      <c r="Q42" s="14" t="s">
         <v>578</v>
       </c>
-      <c r="Q42" s="14" t="s">
+    </row>
+    <row r="43" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
         <v>579</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>30</v>
@@ -7262,45 +7292,45 @@
         <v>130</v>
       </c>
       <c r="F43" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="H43" s="33" t="s">
         <v>582</v>
       </c>
-      <c r="H43" s="33" t="s">
+      <c r="I43" s="33" t="s">
         <v>583</v>
       </c>
-      <c r="I43" s="33" t="s">
+      <c r="J43" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="J43" s="4" t="s">
+      <c r="K43" s="20" t="s">
         <v>585</v>
-      </c>
-      <c r="K43" s="20" t="s">
-        <v>586</v>
       </c>
       <c r="L43" s="22" t="s">
         <v>122</v>
       </c>
       <c r="M43" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="N43" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="N43" s="4" t="s">
-        <v>576</v>
-      </c>
       <c r="O43" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="P43" s="14" t="s">
         <v>587</v>
       </c>
-      <c r="P43" s="14" t="s">
+      <c r="Q43" s="14" t="s">
         <v>588</v>
       </c>
-      <c r="Q43" s="14" t="s">
+    </row>
+    <row r="44" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
         <v>589</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>590</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>30</v>
@@ -7315,45 +7345,45 @@
         <v>233</v>
       </c>
       <c r="F44" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="H44" s="33" t="s">
         <v>592</v>
       </c>
-      <c r="H44" s="33" t="s">
+      <c r="I44" s="33" t="s">
         <v>593</v>
       </c>
-      <c r="I44" s="33" t="s">
+      <c r="J44" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="J44" s="4" t="s">
+      <c r="K44" s="20" t="s">
         <v>595</v>
-      </c>
-      <c r="K44" s="20" t="s">
-        <v>596</v>
       </c>
       <c r="L44" s="22" t="s">
         <v>122</v>
       </c>
       <c r="M44" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="O44" s="14" t="s">
         <v>597</v>
       </c>
-      <c r="N44" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="O44" s="14" t="s">
+      <c r="P44" s="14" t="s">
         <v>598</v>
       </c>
-      <c r="P44" s="14" t="s">
+      <c r="Q44" s="14" t="s">
         <v>599</v>
       </c>
-      <c r="Q44" s="14" t="s">
+    </row>
+    <row r="45" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
         <v>600</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>601</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>30</v>
@@ -7368,45 +7398,45 @@
         <v>246</v>
       </c>
       <c r="F45" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="H45" s="33" t="s">
         <v>603</v>
       </c>
-      <c r="H45" s="33" t="s">
+      <c r="I45" s="33" t="s">
         <v>604</v>
       </c>
-      <c r="I45" s="33" t="s">
+      <c r="J45" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="J45" s="4" t="s">
-        <v>606</v>
-      </c>
       <c r="K45" s="20" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="L45" s="22" t="s">
         <v>122</v>
       </c>
       <c r="M45" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="N45" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="N45" s="4" t="s">
+      <c r="O45" s="14" t="s">
         <v>608</v>
       </c>
-      <c r="O45" s="14" t="s">
+      <c r="P45" s="14" t="s">
         <v>609</v>
       </c>
-      <c r="P45" s="14" t="s">
+      <c r="Q45" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="Q45" s="14" t="s">
+    </row>
+    <row r="46" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
         <v>611</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>12</v>
@@ -7421,19 +7451,19 @@
         <v>110</v>
       </c>
       <c r="F46" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="H46" s="33" t="s">
         <v>614</v>
       </c>
-      <c r="H46" s="33" t="s">
+      <c r="I46" s="33" t="s">
         <v>615</v>
       </c>
-      <c r="I46" s="33" t="s">
+      <c r="J46" s="4" t="s">
         <v>616</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>617</v>
       </c>
       <c r="K46" s="20" t="s">
         <v>110</v>
@@ -7442,24 +7472,24 @@
         <v>110</v>
       </c>
       <c r="M46" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="N46" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="N46" s="4" t="s">
+      <c r="O46" s="14" t="s">
         <v>619</v>
       </c>
-      <c r="O46" s="14" t="s">
+      <c r="P46" s="14" t="s">
         <v>620</v>
       </c>
-      <c r="P46" s="14" t="s">
+      <c r="Q46" s="14" t="s">
         <v>621</v>
       </c>
-      <c r="Q46" s="14" t="s">
+    </row>
+    <row r="47" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
         <v>622</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>623</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>12</v>
@@ -7474,45 +7504,45 @@
         <v>110</v>
       </c>
       <c r="F47" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="G47" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" s="33" t="s">
         <v>625</v>
       </c>
-      <c r="H47" s="33" t="s">
+      <c r="I47" s="33" t="s">
         <v>626</v>
       </c>
-      <c r="I47" s="33" t="s">
+      <c r="J47" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="J47" s="4" t="s">
-        <v>628</v>
-      </c>
       <c r="K47" s="20" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="L47" s="22" t="s">
         <v>122</v>
       </c>
       <c r="M47" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="O47" s="14" t="s">
         <v>629</v>
       </c>
-      <c r="N47" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="O47" s="14" t="s">
+      <c r="P47" s="14" t="s">
         <v>630</v>
       </c>
-      <c r="P47" s="14" t="s">
+      <c r="Q47" s="14" t="s">
         <v>631</v>
       </c>
-      <c r="Q47" s="14" t="s">
+    </row>
+    <row r="48" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
         <v>632</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>12</v>
@@ -7527,45 +7557,45 @@
         <v>110</v>
       </c>
       <c r="F48" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="G48" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="H48" s="33" t="s">
         <v>635</v>
       </c>
-      <c r="H48" s="33" t="s">
+      <c r="I48" s="33" t="s">
         <v>636</v>
       </c>
-      <c r="I48" s="33" t="s">
+      <c r="J48" s="4" t="s">
         <v>637</v>
       </c>
-      <c r="J48" s="4" t="s">
+      <c r="K48" s="20" t="s">
         <v>638</v>
-      </c>
-      <c r="K48" s="20" t="s">
-        <v>639</v>
       </c>
       <c r="L48" s="22" t="s">
         <v>122</v>
       </c>
       <c r="M48" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="N48" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="N48" s="4" t="s">
+      <c r="O48" s="14" t="s">
         <v>641</v>
       </c>
-      <c r="O48" s="14" t="s">
+      <c r="P48" s="14" t="s">
         <v>642</v>
       </c>
-      <c r="P48" s="14" t="s">
+      <c r="Q48" s="14" t="s">
         <v>643</v>
       </c>
-      <c r="Q48" s="14" t="s">
+    </row>
+    <row r="49" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
         <v>644</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>12</v>
@@ -7580,45 +7610,45 @@
         <v>144</v>
       </c>
       <c r="F49" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="G49" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="H49" s="33" t="s">
         <v>647</v>
       </c>
-      <c r="H49" s="33" t="s">
+      <c r="I49" s="33" t="s">
         <v>648</v>
       </c>
-      <c r="I49" s="33" t="s">
+      <c r="J49" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="J49" s="4" t="s">
+      <c r="K49" s="20" t="s">
         <v>650</v>
-      </c>
-      <c r="K49" s="20" t="s">
-        <v>651</v>
       </c>
       <c r="L49" s="22" t="s">
         <v>122</v>
       </c>
       <c r="M49" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="N49" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="N49" s="4" t="s">
+      <c r="O49" s="14" t="s">
         <v>653</v>
       </c>
-      <c r="O49" s="14" t="s">
+      <c r="P49" s="14" t="s">
         <v>654</v>
       </c>
-      <c r="P49" s="14" t="s">
+      <c r="Q49" s="14" t="s">
         <v>655</v>
       </c>
-      <c r="Q49" s="14" t="s">
+    </row>
+    <row r="50" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
         <v>656</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>12</v>
@@ -7633,45 +7663,45 @@
         <v>233</v>
       </c>
       <c r="F50" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="H50" s="33" t="s">
         <v>659</v>
       </c>
-      <c r="H50" s="33" t="s">
+      <c r="I50" s="33" t="s">
         <v>660</v>
       </c>
-      <c r="I50" s="33" t="s">
+      <c r="J50" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="J50" s="4" t="s">
+      <c r="K50" s="20" t="s">
         <v>662</v>
-      </c>
-      <c r="K50" s="20" t="s">
-        <v>663</v>
       </c>
       <c r="L50" s="22" t="s">
         <v>122</v>
       </c>
       <c r="M50" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="N50" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="N50" s="4" t="s">
+      <c r="O50" s="14" t="s">
         <v>665</v>
       </c>
-      <c r="O50" s="14" t="s">
+      <c r="P50" s="14" t="s">
         <v>666</v>
       </c>
-      <c r="P50" s="14" t="s">
+      <c r="Q50" s="14" t="s">
         <v>667</v>
       </c>
-      <c r="Q50" s="14" t="s">
+    </row>
+    <row r="51" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
         <v>668</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>15</v>
@@ -7686,19 +7716,19 @@
         <v>110</v>
       </c>
       <c r="F51" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="H51" s="33" t="s">
         <v>671</v>
       </c>
-      <c r="H51" s="33" t="s">
+      <c r="I51" s="33" t="s">
         <v>672</v>
       </c>
-      <c r="I51" s="33" t="s">
+      <c r="J51" s="4" t="s">
         <v>673</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>674</v>
       </c>
       <c r="K51" s="20" t="s">
         <v>165</v>
@@ -7707,24 +7737,24 @@
         <v>122</v>
       </c>
       <c r="M51" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="N51" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="N51" s="4" t="s">
+      <c r="O51" s="14" t="s">
         <v>676</v>
       </c>
-      <c r="O51" s="14" t="s">
+      <c r="P51" s="14" t="s">
         <v>677</v>
       </c>
-      <c r="P51" s="14" t="s">
+      <c r="Q51" s="14" t="s">
         <v>678</v>
       </c>
-      <c r="Q51" s="14" t="s">
+    </row>
+    <row r="52" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
         <v>679</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>15</v>
@@ -7739,19 +7769,19 @@
         <v>110</v>
       </c>
       <c r="F52" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="H52" s="33" t="s">
         <v>682</v>
       </c>
-      <c r="H52" s="33" t="s">
+      <c r="I52" s="33" t="s">
         <v>683</v>
       </c>
-      <c r="I52" s="33" t="s">
+      <c r="J52" s="4" t="s">
         <v>684</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>685</v>
       </c>
       <c r="K52" s="20" t="s">
         <v>102</v>
@@ -7760,24 +7790,24 @@
         <v>122</v>
       </c>
       <c r="M52" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="N52" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="N52" s="4" t="s">
+      <c r="O52" s="14" t="s">
         <v>687</v>
       </c>
-      <c r="O52" s="14" t="s">
+      <c r="P52" s="14" t="s">
         <v>688</v>
       </c>
-      <c r="P52" s="14" t="s">
+      <c r="Q52" s="14" t="s">
         <v>689</v>
       </c>
-      <c r="Q52" s="14" t="s">
+    </row>
+    <row r="53" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="14" t="s">
         <v>690</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
-        <v>691</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>33</v>
@@ -7792,19 +7822,19 @@
         <v>110</v>
       </c>
       <c r="F53" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="G53" s="14" t="s">
         <v>692</v>
       </c>
-      <c r="G53" s="14" t="s">
+      <c r="H53" t="s">
         <v>693</v>
       </c>
-      <c r="H53" t="s">
+      <c r="I53" t="s">
         <v>694</v>
       </c>
-      <c r="I53" t="s">
+      <c r="J53" s="14" t="s">
         <v>695</v>
-      </c>
-      <c r="J53" s="14" t="s">
-        <v>696</v>
       </c>
       <c r="K53" s="14" t="s">
         <v>110</v>
@@ -7813,24 +7843,24 @@
         <v>110</v>
       </c>
       <c r="M53" s="14" t="s">
+        <v>696</v>
+      </c>
+      <c r="N53" s="14" t="s">
         <v>697</v>
       </c>
-      <c r="N53" s="14" t="s">
+      <c r="O53" s="14" t="s">
         <v>698</v>
       </c>
-      <c r="O53" s="14" t="s">
+      <c r="P53" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="P53" s="14" t="s">
+      <c r="Q53" s="14" t="s">
         <v>700</v>
       </c>
-      <c r="Q53" s="14" t="s">
+    </row>
+    <row r="54" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="14" t="s">
         <v>701</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
-        <v>702</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>33</v>
@@ -7845,45 +7875,45 @@
         <v>110</v>
       </c>
       <c r="F54" s="14" t="s">
+        <v>702</v>
+      </c>
+      <c r="G54" s="14" t="s">
         <v>703</v>
       </c>
-      <c r="G54" s="14" t="s">
+      <c r="H54" t="s">
         <v>704</v>
       </c>
-      <c r="H54" t="s">
+      <c r="I54" t="s">
         <v>705</v>
       </c>
-      <c r="I54" t="s">
+      <c r="J54" s="14" t="s">
         <v>706</v>
       </c>
-      <c r="J54" s="14" t="s">
+      <c r="K54" s="14" t="s">
         <v>707</v>
-      </c>
-      <c r="K54" s="14" t="s">
-        <v>708</v>
       </c>
       <c r="L54" s="14" t="s">
         <v>122</v>
       </c>
       <c r="M54" s="14" t="s">
+        <v>708</v>
+      </c>
+      <c r="N54" s="14" t="s">
         <v>709</v>
       </c>
-      <c r="N54" s="14" t="s">
+      <c r="O54" s="14" t="s">
         <v>710</v>
       </c>
-      <c r="O54" s="14" t="s">
+      <c r="P54" s="14" t="s">
         <v>711</v>
       </c>
-      <c r="P54" s="14" t="s">
+      <c r="Q54" s="14" t="s">
         <v>712</v>
       </c>
-      <c r="Q54" s="14" t="s">
+    </row>
+    <row r="55" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="14" t="s">
         <v>713</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="14" t="s">
-        <v>714</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>33</v>
@@ -7898,42 +7928,42 @@
         <v>110</v>
       </c>
       <c r="F55" s="14" t="s">
+        <v>714</v>
+      </c>
+      <c r="G55" s="14" t="s">
         <v>715</v>
       </c>
-      <c r="G55" s="14" t="s">
+      <c r="I55" t="s">
         <v>716</v>
       </c>
-      <c r="I55" t="s">
+      <c r="J55" s="14" t="s">
         <v>717</v>
       </c>
-      <c r="J55" s="14" t="s">
-        <v>718</v>
-      </c>
       <c r="K55" s="14" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="L55" s="14" t="s">
         <v>136</v>
       </c>
       <c r="M55" s="14" t="s">
+        <v>718</v>
+      </c>
+      <c r="N55" s="14" t="s">
         <v>719</v>
       </c>
-      <c r="N55" s="14" t="s">
+      <c r="O55" s="14" t="s">
         <v>720</v>
       </c>
-      <c r="O55" s="14" t="s">
+      <c r="P55" s="14" t="s">
         <v>721</v>
       </c>
-      <c r="P55" s="14" t="s">
+      <c r="Q55" s="14" t="s">
         <v>722</v>
       </c>
-      <c r="Q55" s="14" t="s">
+    </row>
+    <row r="56" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="14" t="s">
         <v>723</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
-        <v>724</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>33</v>
@@ -7948,42 +7978,42 @@
         <v>110</v>
       </c>
       <c r="F56" s="14" t="s">
+        <v>724</v>
+      </c>
+      <c r="G56" s="14" t="s">
         <v>725</v>
       </c>
-      <c r="G56" s="14" t="s">
+      <c r="I56" t="s">
         <v>726</v>
       </c>
-      <c r="I56" t="s">
+      <c r="J56" s="14" t="s">
         <v>727</v>
       </c>
-      <c r="J56" s="14" t="s">
-        <v>728</v>
-      </c>
       <c r="K56" s="14" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="L56" s="14" t="s">
         <v>122</v>
       </c>
       <c r="M56" s="14" t="s">
+        <v>728</v>
+      </c>
+      <c r="N56" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="N56" s="14" t="s">
+      <c r="O56" s="14" t="s">
         <v>730</v>
       </c>
-      <c r="O56" s="14" t="s">
+      <c r="P56" s="14" t="s">
         <v>731</v>
       </c>
-      <c r="P56" s="14" t="s">
+      <c r="Q56" s="14" t="s">
         <v>732</v>
       </c>
-      <c r="Q56" s="14" t="s">
+    </row>
+    <row r="57" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="14" t="s">
         <v>733</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="14" t="s">
-        <v>734</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>33</v>
@@ -7998,42 +8028,42 @@
         <v>110</v>
       </c>
       <c r="F57" s="14" t="s">
+        <v>734</v>
+      </c>
+      <c r="G57" s="14" t="s">
         <v>735</v>
       </c>
-      <c r="G57" s="14" t="s">
+      <c r="I57" t="s">
         <v>736</v>
       </c>
-      <c r="I57" t="s">
+      <c r="J57" s="14" t="s">
         <v>737</v>
       </c>
-      <c r="J57" s="14" t="s">
+      <c r="K57" s="14" t="s">
         <v>738</v>
-      </c>
-      <c r="K57" s="14" t="s">
-        <v>739</v>
       </c>
       <c r="L57" s="14" t="s">
         <v>122</v>
       </c>
       <c r="M57" s="14" t="s">
+        <v>739</v>
+      </c>
+      <c r="N57" s="14" t="s">
         <v>740</v>
       </c>
-      <c r="N57" s="14" t="s">
+      <c r="O57" s="14" t="s">
         <v>741</v>
       </c>
-      <c r="O57" s="14" t="s">
+      <c r="P57" s="14" t="s">
         <v>742</v>
       </c>
-      <c r="P57" s="14" t="s">
+      <c r="Q57" s="14" t="s">
         <v>743</v>
       </c>
-      <c r="Q57" s="14" t="s">
+    </row>
+    <row r="58" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="14" t="s">
         <v>744</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
-        <v>745</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>33</v>
@@ -8048,48 +8078,48 @@
         <v>144</v>
       </c>
       <c r="F58" s="14" t="s">
+        <v>745</v>
+      </c>
+      <c r="G58" s="14" t="s">
         <v>746</v>
       </c>
-      <c r="G58" s="14" t="s">
+      <c r="I58" t="s">
         <v>747</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" s="14" t="s">
         <v>748</v>
       </c>
-      <c r="J58" s="14" t="s">
+      <c r="K58" s="14" t="s">
         <v>749</v>
-      </c>
-      <c r="K58" s="14" t="s">
-        <v>750</v>
       </c>
       <c r="L58" s="14" t="s">
         <v>122</v>
       </c>
       <c r="M58" s="14" t="s">
+        <v>750</v>
+      </c>
+      <c r="N58" s="14" t="s">
         <v>751</v>
       </c>
-      <c r="N58" s="14" t="s">
+      <c r="O58" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="O58" s="14" t="s">
+      <c r="P58" s="14" t="s">
         <v>753</v>
       </c>
-      <c r="P58" s="14" t="s">
+      <c r="Q58" s="14" t="s">
         <v>754</v>
       </c>
-      <c r="Q58" s="14" t="s">
+    </row>
+    <row r="59" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="14" t="s">
         <v>755</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
-        <v>756</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D59" s="14" t="s">
         <v>220</v>
@@ -8098,48 +8128,48 @@
         <v>130</v>
       </c>
       <c r="F59" s="14" t="s">
+        <v>756</v>
+      </c>
+      <c r="G59" s="14" t="s">
         <v>757</v>
       </c>
-      <c r="G59" s="14" t="s">
+      <c r="I59" t="s">
         <v>758</v>
       </c>
-      <c r="I59" t="s">
+      <c r="J59" s="14" t="s">
         <v>759</v>
       </c>
-      <c r="J59" s="14" t="s">
+      <c r="K59" s="14" t="s">
         <v>760</v>
-      </c>
-      <c r="K59" s="14" t="s">
-        <v>761</v>
       </c>
       <c r="L59" s="14" t="s">
         <v>122</v>
       </c>
       <c r="M59" s="14" t="s">
+        <v>761</v>
+      </c>
+      <c r="N59" s="14" t="s">
         <v>762</v>
       </c>
-      <c r="N59" s="14" t="s">
+      <c r="O59" s="14" t="s">
         <v>763</v>
       </c>
-      <c r="O59" s="14" t="s">
+      <c r="P59" s="14" t="s">
         <v>764</v>
       </c>
-      <c r="P59" s="14" t="s">
+      <c r="Q59" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="Q59" s="14" t="s">
+    </row>
+    <row r="60" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="14" t="s">
         <v>766</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" s="14" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
-        <v>767</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>220</v>
@@ -8148,48 +8178,48 @@
         <v>233</v>
       </c>
       <c r="F60" s="14" t="s">
+        <v>768</v>
+      </c>
+      <c r="G60" s="14" t="s">
         <v>769</v>
       </c>
-      <c r="G60" s="14" t="s">
+      <c r="I60" t="s">
         <v>770</v>
       </c>
-      <c r="I60" t="s">
+      <c r="J60" s="14" t="s">
         <v>771</v>
       </c>
-      <c r="J60" s="14" t="s">
+      <c r="K60" s="14" t="s">
         <v>772</v>
-      </c>
-      <c r="K60" s="14" t="s">
-        <v>773</v>
       </c>
       <c r="L60" s="14" t="s">
         <v>136</v>
       </c>
       <c r="M60" s="14" t="s">
+        <v>773</v>
+      </c>
+      <c r="N60" s="14" t="s">
         <v>774</v>
       </c>
-      <c r="N60" s="14" t="s">
+      <c r="O60" s="14" t="s">
         <v>775</v>
       </c>
-      <c r="O60" s="14" t="s">
+      <c r="P60" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="P60" s="14" t="s">
+      <c r="Q60" s="14" t="s">
         <v>777</v>
       </c>
-      <c r="Q60" s="14" t="s">
+    </row>
+    <row r="61" spans="1:17" s="14" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="14" t="s">
         <v>778</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" s="14" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
-        <v>779</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>232</v>
@@ -8198,48 +8228,48 @@
         <v>246</v>
       </c>
       <c r="F61" s="14" t="s">
+        <v>780</v>
+      </c>
+      <c r="G61" s="14" t="s">
         <v>781</v>
       </c>
-      <c r="G61" s="14" t="s">
+      <c r="I61" t="s">
         <v>782</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61" s="14" t="s">
         <v>783</v>
       </c>
-      <c r="J61" s="14" t="s">
+      <c r="K61" s="14" t="s">
         <v>784</v>
-      </c>
-      <c r="K61" s="14" t="s">
-        <v>785</v>
       </c>
       <c r="L61" s="14" t="s">
         <v>122</v>
       </c>
       <c r="M61" s="14" t="s">
+        <v>785</v>
+      </c>
+      <c r="N61" s="14" t="s">
         <v>786</v>
       </c>
-      <c r="N61" s="14" t="s">
+      <c r="O61" s="14" t="s">
         <v>787</v>
       </c>
-      <c r="O61" s="14" t="s">
+      <c r="P61" s="14" t="s">
         <v>788</v>
       </c>
-      <c r="P61" s="14" t="s">
+      <c r="Q61" s="14" t="s">
         <v>789</v>
       </c>
-      <c r="Q61" s="14" t="s">
+    </row>
+    <row r="62" spans="1:17" ht="144" x14ac:dyDescent="0.2">
+      <c r="A62" s="14" t="s">
         <v>790</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" ht="165" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="s">
-        <v>791</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>36</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D62" s="14" t="s">
         <v>110</v>
@@ -8248,37 +8278,37 @@
         <v>246</v>
       </c>
       <c r="F62" s="14" t="s">
+        <v>791</v>
+      </c>
+      <c r="G62" s="14" t="s">
         <v>792</v>
       </c>
-      <c r="G62" s="14" t="s">
+      <c r="I62" t="s">
         <v>793</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" s="14" t="s">
         <v>794</v>
       </c>
-      <c r="J62" s="14" t="s">
+      <c r="K62" s="14" t="s">
         <v>795</v>
-      </c>
-      <c r="K62" s="14" t="s">
-        <v>796</v>
       </c>
       <c r="L62" s="14" t="s">
         <v>122</v>
       </c>
       <c r="M62" s="14" t="s">
+        <v>796</v>
+      </c>
+      <c r="N62" s="14" t="s">
         <v>797</v>
       </c>
-      <c r="N62" s="14" t="s">
+      <c r="O62" s="14" t="s">
         <v>798</v>
       </c>
-      <c r="O62" s="14" t="s">
+      <c r="P62" s="14" t="s">
         <v>799</v>
       </c>
-      <c r="P62" s="14" t="s">
+      <c r="Q62" s="14" t="s">
         <v>800</v>
-      </c>
-      <c r="Q62" s="14" t="s">
-        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -8290,30 +8320,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D119"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="81.28515625" customWidth="1"/>
+    <col min="3" max="3" width="81.33203125" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="28.140625" customWidth="1"/>
+    <col min="5" max="5" width="28.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
         <v>102</v>
       </c>
@@ -8321,13 +8351,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>102</v>
       </c>
@@ -8335,13 +8365,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="18" t="s">
+        <v>805</v>
+      </c>
+      <c r="D3" s="18" t="s">
         <v>806</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="37" t="s">
         <v>102</v>
       </c>
@@ -8349,13 +8379,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="39" t="s">
+        <v>807</v>
+      </c>
+      <c r="D4" s="39" t="s">
         <v>808</v>
       </c>
-      <c r="D4" s="39" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="34" t="s">
         <v>116</v>
       </c>
@@ -8363,13 +8393,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="s">
+        <v>809</v>
+      </c>
+      <c r="D5" s="36" t="s">
         <v>810</v>
       </c>
-      <c r="D5" s="36" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>116</v>
       </c>
@@ -8377,13 +8407,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="37" t="s">
         <v>116</v>
       </c>
@@ -8391,13 +8421,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D7" s="39" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
         <v>128</v>
       </c>
@@ -8405,13 +8435,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D8" s="36" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
         <v>128</v>
       </c>
@@ -8419,13 +8449,13 @@
         <v>2</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="37" t="s">
         <v>128</v>
       </c>
@@ -8433,13 +8463,13 @@
         <v>3</v>
       </c>
       <c r="C10" s="39" t="s">
+        <v>815</v>
+      </c>
+      <c r="D10" s="39" t="s">
         <v>816</v>
       </c>
-      <c r="D10" s="39" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="34" t="s">
         <v>142</v>
       </c>
@@ -8447,13 +8477,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
         <v>142</v>
       </c>
@@ -8461,13 +8491,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="37" t="s">
         <v>142</v>
       </c>
@@ -8475,13 +8505,13 @@
         <v>3</v>
       </c>
       <c r="C13" s="39" t="s">
+        <v>819</v>
+      </c>
+      <c r="D13" s="39" t="s">
         <v>820</v>
       </c>
-      <c r="D13" s="39" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
         <v>154</v>
       </c>
@@ -8489,13 +8519,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="37" t="s">
         <v>154</v>
       </c>
@@ -8503,55 +8533,55 @@
         <v>2</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D15" s="39" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="34" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B16" s="35">
         <v>1</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B17" s="17">
         <v>2</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="37" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B18" s="38">
         <v>3</v>
       </c>
       <c r="C18" s="39" t="s">
+        <v>826</v>
+      </c>
+      <c r="D18" s="39" t="s">
         <v>827</v>
       </c>
-      <c r="D18" s="39" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="34" t="s">
         <v>165</v>
       </c>
@@ -8559,13 +8589,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
         <v>165</v>
       </c>
@@ -8573,13 +8603,13 @@
         <v>2</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="37" t="s">
         <v>165</v>
       </c>
@@ -8587,13 +8617,13 @@
         <v>3</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="34" t="s">
         <v>175</v>
       </c>
@@ -8601,13 +8631,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
         <v>175</v>
       </c>
@@ -8615,13 +8645,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="37" t="s">
         <v>175</v>
       </c>
@@ -8629,13 +8659,13 @@
         <v>3</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="34" t="s">
         <v>185</v>
       </c>
@@ -8643,13 +8673,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="37" t="s">
         <v>185</v>
       </c>
@@ -8657,13 +8687,13 @@
         <v>2</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="34" t="s">
         <v>196</v>
       </c>
@@ -8671,13 +8701,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D27" s="36" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="37" t="s">
         <v>196</v>
       </c>
@@ -8685,13 +8715,13 @@
         <v>2</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="34" t="s">
         <v>207</v>
       </c>
@@ -8699,13 +8729,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="36" t="s">
+        <v>838</v>
+      </c>
+      <c r="D29" s="36" t="s">
         <v>839</v>
       </c>
-      <c r="D29" s="36" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="37" t="s">
         <v>207</v>
       </c>
@@ -8713,13 +8743,13 @@
         <v>2</v>
       </c>
       <c r="C30" s="39" t="s">
+        <v>840</v>
+      </c>
+      <c r="D30" s="39" t="s">
         <v>841</v>
       </c>
-      <c r="D30" s="39" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="34" t="s">
         <v>218</v>
       </c>
@@ -8727,13 +8757,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="36" t="s">
+        <v>842</v>
+      </c>
+      <c r="D31" s="36" t="s">
         <v>843</v>
       </c>
-      <c r="D31" s="36" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="37" t="s">
         <v>218</v>
       </c>
@@ -8741,13 +8771,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="39" t="s">
+        <v>844</v>
+      </c>
+      <c r="D32" s="39" t="s">
         <v>845</v>
       </c>
-      <c r="D32" s="39" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="34" t="s">
         <v>231</v>
       </c>
@@ -8755,13 +8785,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="36" t="s">
+        <v>846</v>
+      </c>
+      <c r="D33" s="36" t="s">
         <v>847</v>
       </c>
-      <c r="D33" s="36" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="37" t="s">
         <v>231</v>
       </c>
@@ -8769,13 +8799,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D34" s="39" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="34" t="s">
         <v>244</v>
       </c>
@@ -8783,13 +8813,13 @@
         <v>1</v>
       </c>
       <c r="C35" s="36" t="s">
+        <v>849</v>
+      </c>
+      <c r="D35" s="36" t="s">
         <v>850</v>
       </c>
-      <c r="D35" s="36" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="37" t="s">
         <v>244</v>
       </c>
@@ -8797,13 +8827,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="34" t="s">
         <v>257</v>
       </c>
@@ -8811,13 +8841,13 @@
         <v>1</v>
       </c>
       <c r="C37" s="36" t="s">
+        <v>852</v>
+      </c>
+      <c r="D37" s="36" t="s">
         <v>853</v>
       </c>
-      <c r="D37" s="36" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="37" t="s">
         <v>257</v>
       </c>
@@ -8825,13 +8855,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="34" t="s">
         <v>268</v>
       </c>
@@ -8839,13 +8869,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D39" s="36" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="16" t="s">
         <v>268</v>
       </c>
@@ -8853,13 +8883,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="18" t="s">
+        <v>856</v>
+      </c>
+      <c r="D40" s="18" t="s">
         <v>857</v>
       </c>
-      <c r="D40" s="18" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="37" t="s">
         <v>268</v>
       </c>
@@ -8867,13 +8897,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="39" t="s">
+        <v>858</v>
+      </c>
+      <c r="D41" s="39" t="s">
         <v>859</v>
       </c>
-      <c r="D41" s="39" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="34" t="s">
         <v>279</v>
       </c>
@@ -8881,13 +8911,13 @@
         <v>1</v>
       </c>
       <c r="C42" s="36" t="s">
+        <v>860</v>
+      </c>
+      <c r="D42" s="36" t="s">
         <v>861</v>
       </c>
-      <c r="D42" s="36" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="37" t="s">
         <v>279</v>
       </c>
@@ -8895,13 +8925,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="39" t="s">
+        <v>862</v>
+      </c>
+      <c r="D43" s="39" t="s">
         <v>863</v>
       </c>
-      <c r="D43" s="39" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="34" t="s">
         <v>291</v>
       </c>
@@ -8909,13 +8939,13 @@
         <v>1</v>
       </c>
       <c r="C44" s="36" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="16" t="s">
         <v>291</v>
       </c>
@@ -8923,13 +8953,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="37" t="s">
         <v>291</v>
       </c>
@@ -8937,223 +8967,223 @@
         <v>3</v>
       </c>
       <c r="C46" s="39" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D46" s="39" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="34" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B47" s="35">
         <v>1</v>
       </c>
       <c r="C47" s="36" t="s">
+        <v>867</v>
+      </c>
+      <c r="D47" s="36" t="s">
         <v>868</v>
       </c>
-      <c r="D47" s="36" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="37" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B48" s="38">
         <v>2</v>
       </c>
       <c r="C48" s="39" t="s">
+        <v>869</v>
+      </c>
+      <c r="D48" s="39" t="s">
         <v>870</v>
       </c>
-      <c r="D48" s="39" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="34" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B49" s="35">
         <v>1</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="D49" s="36" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="37" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B50" s="38">
         <v>2</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="34" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B51" s="35">
         <v>1</v>
       </c>
       <c r="C51" s="36" t="s">
+        <v>873</v>
+      </c>
+      <c r="D51" s="36" t="s">
         <v>874</v>
       </c>
-      <c r="D51" s="36" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="37" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B52" s="38">
         <v>2</v>
       </c>
       <c r="C52" s="39" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D52" s="39" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="34" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B53" s="35">
         <v>1</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="37" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B54" s="38">
         <v>2</v>
       </c>
       <c r="C54" s="39" t="s">
+        <v>877</v>
+      </c>
+      <c r="D54" s="39" t="s">
         <v>878</v>
       </c>
-      <c r="D54" s="39" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="34" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B55" s="35">
         <v>1</v>
       </c>
       <c r="C55" s="36" t="s">
+        <v>879</v>
+      </c>
+      <c r="D55" s="36" t="s">
         <v>880</v>
       </c>
-      <c r="D55" s="36" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="37" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B56" s="38">
         <v>2</v>
       </c>
       <c r="C56" s="39" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D56" s="39" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="34" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B57" s="35">
         <v>1</v>
       </c>
       <c r="C57" s="36" t="s">
+        <v>882</v>
+      </c>
+      <c r="D57" s="36" t="s">
         <v>883</v>
       </c>
-      <c r="D57" s="36" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="37" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B58" s="38">
         <v>2</v>
       </c>
       <c r="C58" s="39" t="s">
+        <v>884</v>
+      </c>
+      <c r="D58" s="39" t="s">
         <v>885</v>
       </c>
-      <c r="D58" s="39" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="34" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B59" s="35">
         <v>1</v>
       </c>
       <c r="C59" s="36" t="s">
+        <v>886</v>
+      </c>
+      <c r="D59" s="36" t="s">
         <v>887</v>
       </c>
-      <c r="D59" s="36" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="16" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B60" s="17">
         <v>2</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="37" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B61" s="38">
         <v>3</v>
       </c>
       <c r="C61" s="39" t="s">
+        <v>889</v>
+      </c>
+      <c r="D61" s="39" t="s">
         <v>890</v>
       </c>
-      <c r="D61" s="39" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="34" t="s">
         <v>302</v>
       </c>
@@ -9161,13 +9191,13 @@
         <v>1</v>
       </c>
       <c r="C62" s="36" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D62" s="36" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="37" t="s">
         <v>302</v>
       </c>
@@ -9175,13 +9205,13 @@
         <v>2</v>
       </c>
       <c r="C63" s="39" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D63" s="39" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="34" t="s">
         <v>313</v>
       </c>
@@ -9189,13 +9219,13 @@
         <v>1</v>
       </c>
       <c r="C64" s="36" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="37" t="s">
         <v>313</v>
       </c>
@@ -9203,13 +9233,13 @@
         <v>2</v>
       </c>
       <c r="C65" s="39" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D65" s="39" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="34" t="s">
         <v>325</v>
       </c>
@@ -9217,13 +9247,13 @@
         <v>1</v>
       </c>
       <c r="C66" s="36" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D66" s="36" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="37" t="s">
         <v>325</v>
       </c>
@@ -9231,13 +9261,13 @@
         <v>2</v>
       </c>
       <c r="C67" s="39" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D67" s="39" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="34" t="s">
         <v>336</v>
       </c>
@@ -9245,13 +9275,13 @@
         <v>1</v>
       </c>
       <c r="C68" s="36" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D68" s="36" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="16" t="s">
         <v>336</v>
       </c>
@@ -9259,13 +9289,13 @@
         <v>2</v>
       </c>
       <c r="C69" s="18" t="s">
+        <v>898</v>
+      </c>
+      <c r="D69" s="18" t="s">
         <v>899</v>
       </c>
-      <c r="D69" s="18" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="37" t="s">
         <v>336</v>
       </c>
@@ -9273,13 +9303,13 @@
         <v>3</v>
       </c>
       <c r="C70" s="39" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D70" s="39" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="34" t="s">
         <v>348</v>
       </c>
@@ -9287,13 +9317,13 @@
         <v>1</v>
       </c>
       <c r="C71" s="36" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D71" s="36" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="37" t="s">
         <v>348</v>
       </c>
@@ -9301,13 +9331,13 @@
         <v>2</v>
       </c>
       <c r="C72" s="39" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D72" s="39" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="34" t="s">
         <v>359</v>
       </c>
@@ -9315,13 +9345,13 @@
         <v>1</v>
       </c>
       <c r="C73" s="36" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D73" s="36" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="37" t="s">
         <v>359</v>
       </c>
@@ -9329,13 +9359,13 @@
         <v>2</v>
       </c>
       <c r="C74" s="39" t="s">
+        <v>904</v>
+      </c>
+      <c r="D74" s="39" t="s">
         <v>905</v>
       </c>
-      <c r="D74" s="39" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="34" t="s">
         <v>370</v>
       </c>
@@ -9343,13 +9373,13 @@
         <v>1</v>
       </c>
       <c r="C75" s="36" t="s">
+        <v>906</v>
+      </c>
+      <c r="D75" s="36" t="s">
         <v>907</v>
       </c>
-      <c r="D75" s="36" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="37" t="s">
         <v>370</v>
       </c>
@@ -9357,13 +9387,13 @@
         <v>2</v>
       </c>
       <c r="C76" s="39" t="s">
+        <v>908</v>
+      </c>
+      <c r="D76" s="39" t="s">
         <v>909</v>
       </c>
-      <c r="D76" s="39" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="34" t="s">
         <v>382</v>
       </c>
@@ -9371,13 +9401,13 @@
         <v>1</v>
       </c>
       <c r="C77" s="36" t="s">
+        <v>910</v>
+      </c>
+      <c r="D77" s="36" t="s">
         <v>911</v>
       </c>
-      <c r="D77" s="36" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="37" t="s">
         <v>382</v>
       </c>
@@ -9385,13 +9415,13 @@
         <v>2</v>
       </c>
       <c r="C78" s="39" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D78" s="39" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="34" t="s">
         <v>394</v>
       </c>
@@ -9399,13 +9429,13 @@
         <v>1</v>
       </c>
       <c r="C79" s="36" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D79" s="36" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="37" t="s">
         <v>394</v>
       </c>
@@ -9413,13 +9443,13 @@
         <v>2</v>
       </c>
       <c r="C80" s="39" t="s">
+        <v>914</v>
+      </c>
+      <c r="D80" s="39" t="s">
         <v>915</v>
       </c>
-      <c r="D80" s="39" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="34" t="s">
         <v>406</v>
       </c>
@@ -9427,13 +9457,13 @@
         <v>1</v>
       </c>
       <c r="C81" s="36" t="s">
+        <v>916</v>
+      </c>
+      <c r="D81" s="36" t="s">
         <v>917</v>
       </c>
-      <c r="D81" s="36" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="37" t="s">
         <v>406</v>
       </c>
@@ -9441,13 +9471,13 @@
         <v>2</v>
       </c>
       <c r="C82" s="39" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D82" s="39" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="34" t="s">
         <v>418</v>
       </c>
@@ -9455,13 +9485,13 @@
         <v>1</v>
       </c>
       <c r="C83" s="36" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D83" s="36" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="16" t="s">
         <v>418</v>
       </c>
@@ -9469,13 +9499,13 @@
         <v>2</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D84" s="18" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="37" t="s">
         <v>418</v>
       </c>
@@ -9483,13 +9513,13 @@
         <v>3</v>
       </c>
       <c r="C85" s="39" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D85" s="39" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="34" t="s">
         <v>429</v>
       </c>
@@ -9497,13 +9527,13 @@
         <v>1</v>
       </c>
       <c r="C86" s="36" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D86" s="36" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="37" t="s">
         <v>429</v>
       </c>
@@ -9511,13 +9541,13 @@
         <v>2</v>
       </c>
       <c r="C87" s="39" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D87" s="39" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="40" t="s">
         <v>440</v>
       </c>
@@ -9525,13 +9555,13 @@
         <v>1</v>
       </c>
       <c r="C88" s="42" t="s">
+        <v>924</v>
+      </c>
+      <c r="D88" s="42" t="s">
         <v>925</v>
       </c>
-      <c r="D88" s="42" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="15" t="s">
         <v>440</v>
       </c>
@@ -9539,13 +9569,13 @@
         <v>2</v>
       </c>
       <c r="C89" s="44" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D89" s="44" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="45" t="s">
         <v>440</v>
       </c>
@@ -9553,13 +9583,13 @@
         <v>3</v>
       </c>
       <c r="C90" s="47" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D90" s="47" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="34" t="s">
         <v>452</v>
       </c>
@@ -9567,13 +9597,13 @@
         <v>1</v>
       </c>
       <c r="C91" s="36" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D91" s="36" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="16" t="s">
         <v>452</v>
       </c>
@@ -9581,13 +9611,13 @@
         <v>2</v>
       </c>
       <c r="C92" s="18" t="s">
+        <v>929</v>
+      </c>
+      <c r="D92" s="18" t="s">
         <v>930</v>
       </c>
-      <c r="D92" s="18" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="37" t="s">
         <v>452</v>
       </c>
@@ -9595,374 +9625,374 @@
         <v>3</v>
       </c>
       <c r="C93" s="39" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D93" s="39" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D94" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B95">
         <v>2</v>
       </c>
       <c r="C95" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D95" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="34" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B96" s="35">
         <v>1</v>
       </c>
       <c r="C96" s="36" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="37" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B97" s="38">
         <v>2</v>
       </c>
       <c r="C97" s="39" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D97" s="39" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="34" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B98" s="35">
         <v>1</v>
       </c>
       <c r="C98" s="36" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="37" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B99" s="38">
         <v>2</v>
       </c>
       <c r="C99" s="39" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D99" s="39" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="34" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B100" s="35">
         <v>1</v>
       </c>
       <c r="C100" s="36" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D100" s="36" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="37" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B101" s="38">
         <v>2</v>
       </c>
       <c r="C101" s="39" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D101" s="39" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="34" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B102" s="35">
         <v>1</v>
       </c>
       <c r="C102" s="36" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D102" s="36" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="37" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B103" s="38">
         <v>2</v>
       </c>
       <c r="C103" s="39" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D103" s="39" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="34" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B104" s="35">
         <v>1</v>
       </c>
       <c r="C104" s="36" t="s">
+        <v>942</v>
+      </c>
+      <c r="D104" s="36" t="s">
         <v>943</v>
       </c>
-      <c r="D104" s="36" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="37" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B105" s="38">
         <v>2</v>
       </c>
       <c r="C105" s="39" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D105" s="39" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="34" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B106" s="35">
         <v>1</v>
       </c>
       <c r="C106" s="36" t="s">
+        <v>945</v>
+      </c>
+      <c r="D106" s="36" t="s">
         <v>946</v>
       </c>
-      <c r="D106" s="36" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="37" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B107" s="38">
         <v>2</v>
       </c>
       <c r="C107" s="39" t="s">
+        <v>947</v>
+      </c>
+      <c r="D107" s="39" t="s">
         <v>948</v>
       </c>
-      <c r="D107" s="39" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="34" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B108" s="35">
         <v>1</v>
       </c>
       <c r="C108" s="36" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D108" s="36" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="37" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B109" s="38">
         <v>2</v>
       </c>
       <c r="C109" s="39" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="D109" s="39" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="34" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B110" s="35">
         <v>1</v>
       </c>
       <c r="C110" s="36" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="D110" s="36" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="37" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B111" s="38">
         <v>2</v>
       </c>
       <c r="C111" s="39" t="s">
+        <v>952</v>
+      </c>
+      <c r="D111" s="39" t="s">
         <v>953</v>
       </c>
-      <c r="D111" s="39" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="34" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B112" s="35">
         <v>1</v>
       </c>
       <c r="C112" s="36" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D112" s="36" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="37" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B113" s="38">
         <v>2</v>
       </c>
       <c r="C113" s="39" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="D113" s="39" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="34" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B114" s="35">
         <v>1</v>
       </c>
       <c r="C114" s="36" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="D114" s="36" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="37" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B115" s="38">
         <v>2</v>
       </c>
       <c r="C115" s="39" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D115" s="39" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="34" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B116" s="35">
         <v>1</v>
       </c>
       <c r="C116" s="36" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D116" s="36" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="37" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B117" s="38">
         <v>2</v>
       </c>
       <c r="C117" s="39" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D117" s="39" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="34" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B118" s="35">
         <v>1</v>
       </c>
       <c r="C118" s="36" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D118" s="36" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="16" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B119" s="17">
         <v>2</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D119" s="18" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
   </sheetData>
@@ -9974,25 +10004,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="53" defaultRowHeight="408.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="53" defaultRowHeight="409" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.42578125" customWidth="1"/>
-    <col min="6" max="6" width="36.28515625" customWidth="1"/>
-    <col min="7" max="7" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="36.33203125" customWidth="1"/>
+    <col min="7" max="7" width="29.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
+        <v>962</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>963</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="C1" s="25" t="s">
         <v>964</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>965</v>
       </c>
       <c r="D1" s="25" t="s">
         <v>60</v>
@@ -10001,125 +10031,125 @@
         <v>63</v>
       </c>
       <c r="F1" s="25" t="s">
+        <v>965</v>
+      </c>
+      <c r="G1" s="25" t="s">
         <v>966</v>
       </c>
-      <c r="G1" s="25" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
         <v>104</v>
       </c>
       <c r="B2" s="26" t="s">
+        <v>967</v>
+      </c>
+      <c r="C2" s="26" t="s">
         <v>968</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="D2" s="26" t="s">
         <v>969</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="E2" s="26" t="s">
         <v>970</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="F2" s="26" t="s">
         <v>971</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="G2" s="26" t="s">
         <v>972</v>
       </c>
-      <c r="G2" s="26" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="111.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27" t="s">
         <v>117</v>
       </c>
       <c r="B3" s="27" t="s">
+        <v>973</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>974</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="D3" s="27" t="s">
         <v>975</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="E3" s="27" t="s">
         <v>976</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="F3" s="27" t="s">
         <v>977</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="G3" s="27" t="s">
         <v>978</v>
       </c>
-      <c r="G3" s="27" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="28" t="s">
         <v>143</v>
       </c>
       <c r="B4" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="C4" s="28" t="s">
         <v>980</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="D4" s="28" t="s">
         <v>981</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="E4" s="28" t="s">
         <v>982</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="F4" s="28" t="s">
         <v>983</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="G4" s="28" t="s">
         <v>984</v>
       </c>
-      <c r="G4" s="28" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
         <v>220</v>
       </c>
       <c r="B5" s="29" t="s">
+        <v>985</v>
+      </c>
+      <c r="C5" s="29" t="s">
         <v>986</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="D5" s="29" t="s">
         <v>987</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="E5" s="29" t="s">
         <v>988</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="F5" s="29" t="s">
         <v>989</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="G5" s="29" t="s">
         <v>990</v>
       </c>
-      <c r="G5" s="29" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="30" t="s">
         <v>232</v>
       </c>
       <c r="B6" s="30" t="s">
+        <v>991</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>992</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="D6" s="30" t="s">
         <v>993</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="E6" s="30" t="s">
         <v>994</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="F6" s="30" t="s">
         <v>995</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="G6" s="30" t="s">
         <v>996</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>997</v>
       </c>
     </row>
   </sheetData>
@@ -10130,26 +10160,26 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="53" defaultRowHeight="408.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="53" defaultRowHeight="409" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="53" customWidth="1"/>
-    <col min="5" max="5" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.28515625" customWidth="1"/>
-    <col min="7" max="7" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.33203125" customWidth="1"/>
+    <col min="7" max="7" width="29.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
+        <v>962</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>963</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="C1" s="25" t="s">
         <v>964</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>965</v>
       </c>
       <c r="D1" s="25" t="s">
         <v>60</v>
@@ -10158,125 +10188,125 @@
         <v>63</v>
       </c>
       <c r="F1" s="25" t="s">
+        <v>965</v>
+      </c>
+      <c r="G1" s="25" t="s">
         <v>966</v>
       </c>
-      <c r="G1" s="25" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="111.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
         <v>105</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="C2" s="26" t="s">
+        <v>997</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F2" s="26" t="s">
         <v>998</v>
       </c>
-      <c r="D2" s="26" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>1096</v>
-      </c>
-      <c r="F2" s="26" t="s">
+      <c r="G2" s="26" t="s">
         <v>999</v>
       </c>
-      <c r="G2" s="26" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27" t="s">
         <v>130</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C3" s="27" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F3" s="27" t="s">
         <v>1001</v>
       </c>
-      <c r="D3" s="27" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F3" s="27" t="s">
+      <c r="G3" s="27" t="s">
         <v>1002</v>
       </c>
-      <c r="G3" s="27" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="28" t="s">
         <v>144</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C4" s="28" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>1099</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="E4" s="28" t="s">
         <v>1100</v>
       </c>
-      <c r="E4" s="28" t="s">
-        <v>1101</v>
-      </c>
       <c r="F4" s="28" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G4" s="28" t="s">
         <v>1004</v>
       </c>
-      <c r="G4" s="28" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
         <v>233</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C5" s="29" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D5" s="29" t="s">
         <v>1102</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="E5" s="29" t="s">
         <v>1103</v>
       </c>
-      <c r="E5" s="29" t="s">
-        <v>1104</v>
-      </c>
       <c r="F5" s="29" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G5" s="29" t="s">
         <v>1006</v>
       </c>
-      <c r="G5" s="29" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="30" t="s">
         <v>246</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C6" s="30" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D6" s="30" t="s">
         <v>1105</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="E6" s="30" t="s">
         <v>1106</v>
       </c>
-      <c r="E6" s="30" t="s">
-        <v>1107</v>
-      </c>
       <c r="F6" s="30" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G6" s="30" t="s">
         <v>1008</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>1009</v>
       </c>
     </row>
   </sheetData>
@@ -10287,14 +10317,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -10305,7 +10335,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="53" t="s">
         <v>3</v>
       </c>
@@ -10316,7 +10346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="53" t="s">
         <v>6</v>
       </c>
@@ -10327,7 +10357,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="53" t="s">
         <v>9</v>
       </c>
@@ -10338,7 +10368,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="53" t="s">
         <v>12</v>
       </c>
@@ -10349,7 +10379,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="53" t="s">
         <v>15</v>
       </c>
@@ -10360,7 +10390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="53" t="s">
         <v>18</v>
       </c>
@@ -10371,7 +10401,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="53" t="s">
         <v>21</v>
       </c>
@@ -10382,7 +10412,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="53" t="s">
         <v>24</v>
       </c>
@@ -10393,7 +10423,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="53" t="s">
         <v>27</v>
       </c>
@@ -10404,7 +10434,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="53" t="s">
         <v>30</v>
       </c>
@@ -10415,7 +10445,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="64" t="s">
         <v>33</v>
       </c>
@@ -10426,7 +10456,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="64" t="s">
         <v>36</v>
       </c>
@@ -10437,12 +10467,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="49"/>
       <c r="B14" s="49"/>
       <c r="C14" s="49"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="52" t="s">
         <v>39</v>
       </c>
@@ -10453,7 +10483,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="64" t="s">
         <v>42</v>
       </c>
@@ -10464,7 +10494,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="64" t="s">
         <v>45</v>
       </c>
@@ -10475,7 +10505,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="64" t="s">
         <v>48</v>
       </c>
@@ -10486,7 +10516,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="64" t="s">
         <v>51</v>
       </c>
@@ -10497,7 +10527,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="64" t="s">
         <v>54</v>
       </c>
@@ -10508,7 +10538,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="64" t="s">
         <v>57</v>
       </c>
@@ -10519,7 +10549,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="64" t="s">
         <v>60</v>
       </c>
@@ -10530,7 +10560,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="64" t="s">
         <v>63</v>
       </c>
@@ -10541,7 +10571,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="64" t="s">
         <v>66</v>
       </c>
@@ -10552,7 +10582,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="64" t="s">
         <v>69</v>
       </c>
@@ -10563,7 +10593,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="69" t="s">
         <v>72</v>
       </c>
@@ -10574,7 +10604,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="70" t="s">
         <v>75</v>
       </c>
@@ -10585,7 +10615,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="176.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="176" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="70" t="s">
         <v>78</v>
       </c>
@@ -10596,7 +10626,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="64" t="s">
         <v>81</v>
       </c>
@@ -10607,7 +10637,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="64" t="s">
         <v>84</v>
       </c>
@@ -10618,7 +10648,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="64" t="s">
         <v>87</v>
       </c>
@@ -10629,7 +10659,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="64" t="s">
         <v>90</v>
       </c>
@@ -10640,87 +10670,87 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="49"/>
       <c r="B33" s="49"/>
       <c r="C33" s="49"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="49"/>
       <c r="B34" s="49"/>
       <c r="C34" s="49"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="49"/>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="49"/>
       <c r="B36" s="49"/>
       <c r="C36" s="49"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="49"/>
       <c r="B37" s="49"/>
       <c r="C37" s="49"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="49"/>
       <c r="B38" s="49"/>
       <c r="C38" s="49"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="49"/>
       <c r="B39" s="49"/>
       <c r="C39" s="49"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="49"/>
       <c r="B40" s="49"/>
       <c r="C40" s="49"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="49"/>
       <c r="B41" s="49"/>
       <c r="C41" s="49"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="49"/>
       <c r="B42" s="49"/>
       <c r="C42" s="49"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="49"/>
       <c r="B43" s="49"/>
       <c r="C43" s="49"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="49"/>
       <c r="B44" s="49"/>
       <c r="C44" s="49"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="49"/>
       <c r="B45" s="49"/>
       <c r="C45" s="49"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="49"/>
       <c r="B46" s="49"/>
       <c r="C46" s="49"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="49"/>
       <c r="B47" s="49"/>
       <c r="C47" s="49"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="49"/>
       <c r="B48" s="49"/>
       <c r="C48" s="49"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="49"/>
       <c r="B49" s="49"/>
       <c r="C49" s="49"/>
@@ -10733,45 +10763,45 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="71" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B1" s="71" t="s">
         <v>1010</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="C1" s="49"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="64" t="s">
         <v>1011</v>
-      </c>
-      <c r="C1" s="49"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
-        <v>1012</v>
       </c>
       <c r="B2" s="72">
         <v>61</v>
       </c>
       <c r="C2" s="49"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="49"/>
       <c r="B3" s="49"/>
       <c r="C3" s="49"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="48" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B4" s="71" t="s">
         <v>1013</v>
       </c>
-      <c r="B4" s="71" t="s">
-        <v>1014</v>
-      </c>
       <c r="C4" s="49"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="73" t="s">
         <v>3</v>
       </c>
@@ -10780,7 +10810,7 @@
       </c>
       <c r="C5" s="49"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="75" t="s">
         <v>6</v>
       </c>
@@ -10789,7 +10819,7 @@
       </c>
       <c r="C6" s="49"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="76" t="s">
         <v>9</v>
       </c>
@@ -10798,7 +10828,7 @@
       </c>
       <c r="C7" s="49"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="77" t="s">
         <v>18</v>
       </c>
@@ -10807,7 +10837,7 @@
       </c>
       <c r="C8" s="49"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="78" t="s">
         <v>21</v>
       </c>
@@ -10816,7 +10846,7 @@
       </c>
       <c r="C9" s="49"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="79" t="s">
         <v>24</v>
       </c>
@@ -10825,7 +10855,7 @@
       </c>
       <c r="C10" s="49"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="80" t="s">
         <v>27</v>
       </c>
@@ -10834,7 +10864,7 @@
       </c>
       <c r="C11" s="49"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="81" t="s">
         <v>30</v>
       </c>
@@ -10843,7 +10873,7 @@
       </c>
       <c r="C12" s="49"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="82" t="s">
         <v>12</v>
       </c>
@@ -10852,7 +10882,7 @@
       </c>
       <c r="C13" s="49"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="83" t="s">
         <v>15</v>
       </c>
@@ -10861,7 +10891,7 @@
       </c>
       <c r="C14" s="49"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="84" t="s">
         <v>33</v>
       </c>
@@ -10870,7 +10900,7 @@
       </c>
       <c r="C15" s="49"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="85" t="s">
         <v>36</v>
       </c>
@@ -10879,181 +10909,181 @@
       </c>
       <c r="C16" s="49"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="49"/>
       <c r="B17" s="49"/>
       <c r="C17" s="49"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="48" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B18" s="71" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C18" s="49"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="76" t="s">
         <v>1015</v>
-      </c>
-      <c r="B18" s="71" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C18" s="49"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="76" t="s">
-        <v>1016</v>
       </c>
       <c r="B19" s="74">
         <v>17</v>
       </c>
       <c r="C19" s="49"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="86" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B20" s="74">
         <v>29</v>
       </c>
       <c r="C20" s="49"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="73" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B21" s="74">
         <v>14</v>
       </c>
       <c r="C21" s="49"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="85" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B22" s="74">
         <v>1</v>
       </c>
       <c r="C22" s="49"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="49"/>
       <c r="B23" s="49"/>
       <c r="C23" s="49"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="48" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B24" s="71" t="s">
         <v>1020</v>
       </c>
-      <c r="B24" s="71" t="s">
+      <c r="C24" s="49"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="49" t="s">
         <v>1021</v>
-      </c>
-      <c r="C24" s="49"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="49" t="s">
-        <v>1022</v>
       </c>
       <c r="B25" s="74">
         <v>8</v>
       </c>
       <c r="C25" s="49"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="49" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B26" s="74">
         <v>11</v>
       </c>
       <c r="C26" s="49"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="49" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B27" s="74">
         <v>13</v>
       </c>
       <c r="C27" s="49"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="49" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B28" s="74">
         <v>8</v>
       </c>
       <c r="C28" s="49"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="49" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B29" s="74">
         <v>6</v>
       </c>
       <c r="C29" s="49"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="49" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B30" s="74">
         <v>4</v>
       </c>
       <c r="C30" s="49"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="49" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B31" s="74">
         <v>6</v>
       </c>
       <c r="C31" s="49"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="49" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B32" s="74">
         <v>10</v>
       </c>
       <c r="C32" s="49"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="49" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B33" s="74">
         <v>7</v>
       </c>
       <c r="C33" s="49"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="49" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B34" s="74">
         <v>4</v>
       </c>
       <c r="C34" s="49"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="49"/>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="49"/>
       <c r="B36" s="49"/>
       <c r="C36" s="49"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="49"/>
       <c r="B37" s="49"/>
       <c r="C37" s="49"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="49"/>
       <c r="B38" s="49"/>
       <c r="C38" s="49"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="49"/>
       <c r="B39" s="49"/>
       <c r="C39" s="49"/>
@@ -11065,242 +11095,259 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="6" max="6" width="48.33203125" customWidth="1"/>
     <col min="7" max="7" width="38" customWidth="1"/>
     <col min="8" max="9" width="45" customWidth="1"/>
     <col min="10" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="87" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B1" s="87" t="s">
         <v>1032</v>
       </c>
-      <c r="B1" s="87" t="s">
+      <c r="C1" s="87" t="s">
         <v>1033</v>
       </c>
-      <c r="C1" s="87" t="s">
+      <c r="D1" s="87" t="s">
         <v>1034</v>
       </c>
-      <c r="D1" s="87" t="s">
+      <c r="E1" s="87" t="s">
         <v>1035</v>
       </c>
-      <c r="E1" s="87" t="s">
+      <c r="F1" s="87" t="s">
         <v>1036</v>
       </c>
-      <c r="F1" s="87" t="s">
+      <c r="G1" s="87" t="s">
         <v>1037</v>
       </c>
-      <c r="G1" s="87" t="s">
+      <c r="H1" s="87" t="s">
         <v>1038</v>
       </c>
-      <c r="H1" s="87" t="s">
+      <c r="I1" s="87" t="s">
         <v>1039</v>
       </c>
-      <c r="I1" s="87" t="s">
+      <c r="J1" s="87" t="s">
         <v>1040</v>
       </c>
-      <c r="J1" s="87" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="88" t="s">
         <v>1041</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="88" t="s">
+      <c r="B2" s="89" t="s">
         <v>1042</v>
       </c>
-      <c r="B2" s="89" t="s">
+      <c r="C2" s="90" t="s">
         <v>1043</v>
       </c>
-      <c r="C2" s="90" t="s">
+      <c r="D2" s="89" t="s">
         <v>1044</v>
       </c>
-      <c r="D2" s="89" t="s">
+      <c r="E2" s="91" t="s">
         <v>1045</v>
       </c>
-      <c r="E2" s="91" t="s">
+      <c r="F2" s="91" t="s">
         <v>1046</v>
       </c>
-      <c r="F2" s="91" t="s">
+      <c r="G2" s="91" t="s">
         <v>1047</v>
       </c>
-      <c r="G2" s="91" t="s">
+      <c r="H2" s="91" t="s">
         <v>1048</v>
       </c>
-      <c r="H2" s="91" t="s">
+      <c r="I2" s="91" t="s">
         <v>1049</v>
       </c>
-      <c r="I2" s="91" t="s">
+      <c r="J2" s="91" t="s">
         <v>1050</v>
       </c>
-      <c r="J2" s="91" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="88" t="s">
         <v>1051</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="88" t="s">
+      <c r="B3" s="89" t="s">
         <v>1052</v>
       </c>
-      <c r="B3" s="89" t="s">
+      <c r="C3" s="92" t="s">
         <v>1053</v>
       </c>
-      <c r="C3" s="92" t="s">
+      <c r="D3" s="89" t="s">
         <v>1054</v>
       </c>
-      <c r="D3" s="89" t="s">
+      <c r="E3" s="91" t="s">
         <v>1055</v>
       </c>
-      <c r="E3" s="91" t="s">
+      <c r="F3" s="91" t="s">
         <v>1056</v>
       </c>
-      <c r="F3" s="91" t="s">
+      <c r="G3" s="91" t="s">
         <v>1057</v>
       </c>
-      <c r="G3" s="91" t="s">
+      <c r="H3" s="91" t="s">
         <v>1058</v>
       </c>
-      <c r="H3" s="91" t="s">
+      <c r="I3" s="91" t="s">
         <v>1059</v>
       </c>
-      <c r="I3" s="91" t="s">
+      <c r="J3" s="91" t="s">
         <v>1060</v>
       </c>
-      <c r="J3" s="91" t="s">
+    </row>
+    <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="88" t="s">
         <v>1061</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="88" t="s">
+      <c r="B4" s="89" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C4" s="92" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D4" s="89" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E4" s="91" t="s">
         <v>1062</v>
       </c>
-      <c r="B4" s="89" t="s">
+      <c r="F4" s="91" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G4" s="91" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H4" s="91" t="s">
+        <v>1065</v>
+      </c>
+      <c r="I4" s="91" t="s">
+        <v>1066</v>
+      </c>
+      <c r="J4" s="91" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="88" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B5" s="89" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C5" s="92" t="s">
         <v>1053</v>
       </c>
-      <c r="C4" s="92" t="s">
+      <c r="D5" s="89" t="s">
         <v>1054</v>
       </c>
-      <c r="D4" s="89" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E4" s="91" t="s">
-        <v>1063</v>
-      </c>
-      <c r="F4" s="91" t="s">
-        <v>1064</v>
-      </c>
-      <c r="G4" s="91" t="s">
-        <v>1065</v>
-      </c>
-      <c r="H4" s="91" t="s">
-        <v>1066</v>
-      </c>
-      <c r="I4" s="91" t="s">
-        <v>1067</v>
-      </c>
-      <c r="J4" s="91" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="88" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B5" s="89" t="s">
+      <c r="E5" s="91" t="s">
         <v>1070</v>
       </c>
-      <c r="C5" s="92" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D5" s="89" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E5" s="91" t="s">
+      <c r="F5" s="91" t="s">
         <v>1071</v>
       </c>
-      <c r="F5" s="91" t="s">
+      <c r="G5" s="91" t="s">
         <v>1072</v>
       </c>
-      <c r="G5" s="91" t="s">
+      <c r="H5" s="91" t="s">
         <v>1073</v>
       </c>
-      <c r="H5" s="91" t="s">
+      <c r="I5" s="91" t="s">
         <v>1074</v>
       </c>
-      <c r="I5" s="91" t="s">
+      <c r="J5" s="91" t="s">
         <v>1075</v>
       </c>
-      <c r="J5" s="91" t="s">
+    </row>
+    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="88" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="88" t="s">
+      <c r="B6" s="89" t="s">
         <v>1077</v>
       </c>
-      <c r="B6" s="89" t="s">
+      <c r="C6" s="92" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D6" s="89" t="s">
         <v>1078</v>
       </c>
-      <c r="C6" s="92" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D6" s="89" t="s">
+      <c r="E6" s="91" t="s">
         <v>1079</v>
       </c>
-      <c r="E6" s="91" t="s">
+      <c r="F6" s="91" t="s">
         <v>1080</v>
       </c>
-      <c r="F6" s="91" t="s">
+      <c r="G6" s="91" t="s">
         <v>1081</v>
       </c>
-      <c r="G6" s="91" t="s">
+      <c r="H6" s="91" t="s">
         <v>1082</v>
       </c>
-      <c r="H6" s="91" t="s">
+      <c r="I6" s="91" t="s">
         <v>1083</v>
       </c>
-      <c r="I6" s="91" t="s">
+      <c r="J6" s="91" t="s">
         <v>1084</v>
       </c>
-      <c r="J6" s="91" t="s">
+    </row>
+    <row r="7" spans="1:10" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="88" t="s">
         <v>1085</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="88" t="s">
+      <c r="B7" s="89" t="s">
         <v>1086</v>
       </c>
-      <c r="B7" s="89" t="s">
+      <c r="C7" s="93" t="s">
         <v>1087</v>
       </c>
-      <c r="C7" s="93" t="s">
+      <c r="D7" s="89" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E7" s="91" t="s">
         <v>1088</v>
       </c>
-      <c r="D7" s="89" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E7" s="91" t="s">
+      <c r="F7" s="91" t="s">
         <v>1089</v>
       </c>
-      <c r="F7" s="91" t="s">
+      <c r="G7" s="91" t="s">
         <v>1090</v>
       </c>
-      <c r="G7" s="91" t="s">
+      <c r="H7" s="91" t="s">
         <v>1091</v>
       </c>
-      <c r="H7" s="91" t="s">
+      <c r="I7" s="91" t="s">
         <v>1092</v>
       </c>
-      <c r="I7" s="91" t="s">
+      <c r="J7" s="91" t="s">
         <v>1093</v>
       </c>
-      <c r="J7" s="91" t="s">
-        <v>1094</v>
+    </row>
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.2">
+      <c r="B8" s="89" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C8" s="94" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D8" s="95" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E8" s="91" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F8" s="96" t="s">
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
